--- a/Excel/PhantomAttrConfig.xlsx
+++ b/Excel/PhantomAttrConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -1614,7 +1614,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="1">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="G6" s="1">
         <v>1000</v>
@@ -1682,7 +1682,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="1">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="G7" s="1">
         <v>50000</v>
@@ -1750,7 +1750,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="1">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="G8" s="1">
         <v>40000</v>
@@ -1818,7 +1818,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="1">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="G9" s="1">
         <v>100000</v>
@@ -1886,7 +1886,7 @@
         <v>1</v>
       </c>
       <c r="F10" s="1">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="G10" s="1">
         <v>100000</v>
@@ -1954,7 +1954,7 @@
         <v>1</v>
       </c>
       <c r="F11" s="1">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="G11" s="1">
         <v>100000</v>
@@ -2022,7 +2022,7 @@
         <v>1</v>
       </c>
       <c r="F12" s="1">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>44</v>
@@ -2099,7 +2099,7 @@
         <v>1</v>
       </c>
       <c r="F13" s="1">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="G13" s="6" t="s">
         <v>45</v>
@@ -2176,7 +2176,7 @@
         <v>1</v>
       </c>
       <c r="F14" s="1">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="G14" s="6" t="s">
         <v>45</v>
@@ -2253,7 +2253,7 @@
         <v>1</v>
       </c>
       <c r="F15" s="1">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>45</v>
@@ -2321,7 +2321,7 @@
         <v>1</v>
       </c>
       <c r="F16" s="1">
-        <v>500</v>
+        <v>750</v>
       </c>
       <c r="G16" s="6" t="s">
         <v>45</v>
@@ -2389,7 +2389,7 @@
         <v>1</v>
       </c>
       <c r="F17" s="1">
-        <v>500</v>
+        <v>750</v>
       </c>
       <c r="G17" s="6" t="s">
         <v>45</v>
@@ -2457,7 +2457,7 @@
         <v>1</v>
       </c>
       <c r="F18" s="1">
-        <v>500</v>
+        <v>750</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>45</v>
@@ -2525,7 +2525,7 @@
         <v>1</v>
       </c>
       <c r="F19" s="1">
-        <v>500</v>
+        <v>750</v>
       </c>
       <c r="G19" s="6" t="s">
         <v>68</v>
@@ -2593,7 +2593,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1">
-        <v>500</v>
+        <v>750</v>
       </c>
       <c r="G20" s="6" t="s">
         <v>68</v>
@@ -2661,7 +2661,7 @@
         <v>1</v>
       </c>
       <c r="F21" s="1">
-        <v>500</v>
+        <v>750</v>
       </c>
       <c r="G21" s="6" t="s">
         <v>68</v>
@@ -2720,7 +2720,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="D3 E3 F3 G3 H3 I3 J3 K3 L3 M3 O3 P3 Q3 R3 S3 T3 U3 V3 W3 D4 E4 F4 G4 H4 I4 J4 K4 L4 M4 O4 P4 Q4 R4 S4 T4 U4 V4 W4 D5 E5 F5 G5 H5 I5 J5 K5 L5 M5 N5 O5 P5 Q5 R5 S5 T5 U5 V5 W5 C3:C5 N3:N4" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="D3:M3 O3:W3 P4:W4 P5:W5 C3:C5 N3:N5 O4:O5 D4:M5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/PhantomAttrConfig.xlsx
+++ b/Excel/PhantomAttrConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -2022,7 +2022,7 @@
         <v>1</v>
       </c>
       <c r="F12" s="1">
-        <v>500</v>
+        <v>750</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>44</v>
@@ -2099,7 +2099,7 @@
         <v>1</v>
       </c>
       <c r="F13" s="1">
-        <v>500</v>
+        <v>750</v>
       </c>
       <c r="G13" s="6" t="s">
         <v>45</v>
@@ -2176,7 +2176,7 @@
         <v>1</v>
       </c>
       <c r="F14" s="1">
-        <v>500</v>
+        <v>750</v>
       </c>
       <c r="G14" s="6" t="s">
         <v>45</v>
@@ -2253,7 +2253,7 @@
         <v>1</v>
       </c>
       <c r="F15" s="1">
-        <v>500</v>
+        <v>750</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>45</v>
@@ -2720,7 +2720,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="D3:M3 O3:W3 P4:W4 P5:W5 C3:C5 N3:N5 O4:O5 D4:M5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:W5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/PhantomAttrConfig.xlsx
+++ b/Excel/PhantomAttrConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -1614,7 +1614,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="1">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G6" s="1">
         <v>1000</v>
@@ -1682,7 +1682,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="1">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G7" s="1">
         <v>50000</v>
@@ -1750,7 +1750,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="1">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G8" s="1">
         <v>40000</v>
@@ -1818,7 +1818,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="1">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G9" s="1">
         <v>100000</v>
@@ -1886,7 +1886,7 @@
         <v>1</v>
       </c>
       <c r="F10" s="1">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G10" s="1">
         <v>100000</v>
@@ -1954,7 +1954,7 @@
         <v>1</v>
       </c>
       <c r="F11" s="1">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G11" s="1">
         <v>100000</v>
@@ -2022,7 +2022,7 @@
         <v>1</v>
       </c>
       <c r="F12" s="1">
-        <v>750</v>
+        <v>2000</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>44</v>
@@ -2099,7 +2099,7 @@
         <v>1</v>
       </c>
       <c r="F13" s="1">
-        <v>750</v>
+        <v>2000</v>
       </c>
       <c r="G13" s="6" t="s">
         <v>45</v>
@@ -2176,7 +2176,7 @@
         <v>1</v>
       </c>
       <c r="F14" s="1">
-        <v>750</v>
+        <v>2000</v>
       </c>
       <c r="G14" s="6" t="s">
         <v>45</v>
@@ -2253,7 +2253,7 @@
         <v>1</v>
       </c>
       <c r="F15" s="1">
-        <v>750</v>
+        <v>2000</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>45</v>
@@ -2321,7 +2321,7 @@
         <v>1</v>
       </c>
       <c r="F16" s="1">
-        <v>750</v>
+        <v>2000</v>
       </c>
       <c r="G16" s="6" t="s">
         <v>45</v>
@@ -2389,7 +2389,7 @@
         <v>1</v>
       </c>
       <c r="F17" s="1">
-        <v>750</v>
+        <v>2000</v>
       </c>
       <c r="G17" s="6" t="s">
         <v>45</v>
@@ -2457,7 +2457,7 @@
         <v>1</v>
       </c>
       <c r="F18" s="1">
-        <v>750</v>
+        <v>2000</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>45</v>
@@ -2525,7 +2525,7 @@
         <v>1</v>
       </c>
       <c r="F19" s="1">
-        <v>750</v>
+        <v>2000</v>
       </c>
       <c r="G19" s="6" t="s">
         <v>68</v>
@@ -2593,7 +2593,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1">
-        <v>750</v>
+        <v>2000</v>
       </c>
       <c r="G20" s="6" t="s">
         <v>68</v>
@@ -2661,7 +2661,7 @@
         <v>1</v>
       </c>
       <c r="F21" s="1">
-        <v>750</v>
+        <v>2000</v>
       </c>
       <c r="G21" s="6" t="s">
         <v>68</v>

--- a/Excel/PhantomAttrConfig.xlsx
+++ b/Excel/PhantomAttrConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -32,7 +32,7 @@
     <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="P3" authorId="0">
+    <comment ref="X3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -57,7 +57,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AB3" authorId="0">
+    <comment ref="AP3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -86,7 +86,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="107">
   <si>
     <t>ID</t>
   </si>
@@ -103,13 +103,37 @@
     <t>Attr</t>
   </si>
   <si>
+    <t>AttrRise</t>
+  </si>
+  <si>
     <t>Def</t>
   </si>
   <si>
+    <t>DefRise</t>
+  </si>
+  <si>
     <t>Hp</t>
   </si>
   <si>
-    <t>AttrRise</t>
+    <t>HpRise</t>
+  </si>
+  <si>
+    <t>DamageMul</t>
+  </si>
+  <si>
+    <t>MulRise</t>
+  </si>
+  <si>
+    <t>Strong</t>
+  </si>
+  <si>
+    <t>StrongRise</t>
+  </si>
+  <si>
+    <t>Parray</t>
+  </si>
+  <si>
+    <t>ParrayRise</t>
   </si>
   <si>
     <t>DamageIncrea</t>
@@ -145,6 +169,24 @@
     <t>AttrRiseList</t>
   </si>
   <si>
+    <t>Speed</t>
+  </si>
+  <si>
+    <t>SpeedRise</t>
+  </si>
+  <si>
+    <t>Accuracy</t>
+  </si>
+  <si>
+    <t>AccuracyRise</t>
+  </si>
+  <si>
+    <t>Miss</t>
+  </si>
+  <si>
+    <t>MissRise</t>
+  </si>
+  <si>
     <t>RewardId</t>
   </si>
   <si>
@@ -305,19 +347,80 @@
   </si>
   <si>
     <t>爆伤</t>
+  </si>
+  <si>
+    <t>1E+60</t>
+  </si>
+  <si>
+    <t>1E+100</t>
+  </si>
+  <si>
+    <t>1E+1</t>
+  </si>
+  <si>
+    <t>1E+10</t>
+  </si>
+  <si>
+    <t>1012,2003,2007,3008</t>
+  </si>
+  <si>
+    <t>1004,2009,2007,1012</t>
+  </si>
+  <si>
+    <t>物理倍率</t>
+  </si>
+  <si>
+    <t>魔法倍率</t>
+  </si>
+  <si>
+    <t>道士倍率</t>
+  </si>
+  <si>
+    <t>1E+70</t>
+  </si>
+  <si>
+    <t>1E+20</t>
+  </si>
+  <si>
+    <t>物伤倍率</t>
+  </si>
+  <si>
+    <t>魔伤倍率</t>
+  </si>
+  <si>
+    <t>道伤倍率</t>
+  </si>
+  <si>
+    <t>1E+80</t>
+  </si>
+  <si>
+    <t>1E+30</t>
+  </si>
+  <si>
+    <t>增伤倍率</t>
+  </si>
+  <si>
+    <t>1E+90</t>
+  </si>
+  <si>
+    <t>1E+40</t>
+  </si>
+  <si>
+    <t>破韧倍率</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -333,6 +436,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <color theme="1"/>
@@ -341,6 +450,7 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <color theme="1"/>
       <name val="等线"/>
@@ -826,146 +936,166 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1285,37 +1415,48 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AD21"/>
+  <dimension ref="A1:AR39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="9" style="2"/>
     <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
     <col min="4" max="6" width="12.125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="19.625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="18" style="2" customWidth="1"/>
-    <col min="9" max="9" width="26" style="2" customWidth="1"/>
-    <col min="10" max="10" width="9.5" style="2" customWidth="1"/>
-    <col min="11" max="11" width="12.25" style="2" customWidth="1"/>
-    <col min="12" max="12" width="5.625" style="2" customWidth="1"/>
-    <col min="13" max="13" width="5.875" style="2" customWidth="1"/>
-    <col min="14" max="14" width="6.5" style="2" customWidth="1"/>
-    <col min="15" max="15" width="5.875" style="2" customWidth="1"/>
-    <col min="16" max="18" width="8.25" style="2" customWidth="1"/>
-    <col min="19" max="19" width="14.5" style="2" customWidth="1"/>
-    <col min="20" max="21" width="15.125" style="2" customWidth="1"/>
-    <col min="22" max="22" width="12.5" style="2" customWidth="1"/>
-    <col min="23" max="23" width="13" style="2" customWidth="1"/>
-    <col min="24" max="24" width="13.375" style="1" customWidth="1"/>
-    <col min="25" max="25" width="11.5" style="1" customWidth="1"/>
-    <col min="26" max="26" width="13.375" style="1" customWidth="1"/>
-    <col min="27" max="28" width="30.125" style="1" customWidth="1"/>
-    <col min="29" max="29" width="8.125" style="2" customWidth="1"/>
-    <col min="30" max="30" width="9.625" style="2" customWidth="1"/>
-    <col min="31" max="16384" width="9" style="2"/>
+    <col min="7" max="7" width="14.25" style="2" customWidth="1"/>
+    <col min="8" max="8" width="9.25" style="2" customWidth="1"/>
+    <col min="9" max="9" width="16" style="2" customWidth="1"/>
+    <col min="10" max="10" width="12.75" style="2" customWidth="1"/>
+    <col min="11" max="11" width="14" style="2" customWidth="1"/>
+    <col min="12" max="12" width="10.6666666666667" style="2" customWidth="1"/>
+    <col min="13" max="13" width="9.91666666666667" style="3" customWidth="1"/>
+    <col min="14" max="14" width="7.125" style="3" customWidth="1"/>
+    <col min="15" max="15" width="8.66666666666667" style="3" customWidth="1"/>
+    <col min="16" max="18" width="8.41666666666667" style="3" customWidth="1"/>
+    <col min="19" max="19" width="12.25" style="2" customWidth="1"/>
+    <col min="20" max="20" width="10.5" style="2" customWidth="1"/>
+    <col min="21" max="21" width="7.58333333333333" style="2" customWidth="1"/>
+    <col min="22" max="22" width="10.5" style="2" customWidth="1"/>
+    <col min="23" max="23" width="12.6666666666667" style="2" customWidth="1"/>
+    <col min="24" max="26" width="8.25" style="2" customWidth="1"/>
+    <col min="27" max="27" width="10.75" style="2" customWidth="1"/>
+    <col min="28" max="28" width="10.8333333333333" style="2" customWidth="1"/>
+    <col min="29" max="29" width="9.08333333333333" style="2" customWidth="1"/>
+    <col min="30" max="31" width="8.625" style="3" customWidth="1"/>
+    <col min="32" max="32" width="10.5083333333333" style="3" customWidth="1"/>
+    <col min="33" max="33" width="8.76666666666667" style="3" customWidth="1"/>
+    <col min="34" max="35" width="9.25" style="3" customWidth="1"/>
+    <col min="36" max="36" width="12.5" style="2" customWidth="1"/>
+    <col min="37" max="37" width="13" style="2" customWidth="1"/>
+    <col min="38" max="38" width="13.375" style="1" customWidth="1"/>
+    <col min="39" max="39" width="15.9166666666667" style="1" customWidth="1"/>
+    <col min="40" max="40" width="29.3333333333333" style="1" customWidth="1"/>
+    <col min="41" max="42" width="30.125" style="1" customWidth="1"/>
+    <col min="43" max="43" width="8.125" style="2" customWidth="1"/>
+    <col min="44" max="44" width="9.625" style="2" customWidth="1"/>
+    <col min="45" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:30">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:44">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="G1" s="2"/>
@@ -1324,21 +1465,35 @@
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
       <c r="S1" s="2"/>
       <c r="T1" s="2"/>
       <c r="U1" s="2"/>
       <c r="V1" s="2"/>
       <c r="W1" s="2"/>
+      <c r="X1" s="2"/>
+      <c r="Y1" s="2"/>
+      <c r="Z1" s="2"/>
+      <c r="AA1" s="2"/>
+      <c r="AB1" s="2"/>
       <c r="AC1" s="2"/>
-      <c r="AD1" s="2"/>
+      <c r="AD1" s="3"/>
+      <c r="AE1" s="3"/>
+      <c r="AF1" s="3"/>
+      <c r="AG1" s="3"/>
+      <c r="AH1" s="3"/>
+      <c r="AI1" s="3"/>
+      <c r="AJ1" s="2"/>
+      <c r="AK1" s="2"/>
+      <c r="AQ1" s="2"/>
+      <c r="AR1" s="2"/>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:30">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:44">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="G2" s="2"/>
@@ -1347,84 +1502,98 @@
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
-      <c r="Q2" s="2"/>
-      <c r="R2" s="2"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
       <c r="S2" s="2"/>
       <c r="T2" s="2"/>
       <c r="U2" s="2"/>
       <c r="V2" s="2"/>
       <c r="W2" s="2"/>
+      <c r="X2" s="2"/>
+      <c r="Y2" s="2"/>
+      <c r="Z2" s="2"/>
+      <c r="AA2" s="2"/>
+      <c r="AB2" s="2"/>
       <c r="AC2" s="2"/>
-      <c r="AD2" s="2"/>
+      <c r="AD2" s="3"/>
+      <c r="AE2" s="3"/>
+      <c r="AF2" s="3"/>
+      <c r="AG2" s="3"/>
+      <c r="AH2" s="3"/>
+      <c r="AI2" s="3"/>
+      <c r="AJ2" s="2"/>
+      <c r="AK2" s="2"/>
+      <c r="AQ2" s="2"/>
+      <c r="AR2" s="2"/>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:30">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:44">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
-      <c r="C3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="3" t="s">
+      <c r="C3" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I3" s="3" t="s">
+      <c r="H3" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="L3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="M3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="N3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="O3" s="3" t="s">
+      <c r="O3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="P3" s="3" t="s">
+      <c r="P3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="Q3" s="3" t="s">
+      <c r="Q3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="R3" s="3" t="s">
+      <c r="R3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="S3" s="3" t="s">
+      <c r="S3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="T3" s="3" t="s">
+      <c r="T3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="U3" s="3" t="s">
+      <c r="U3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="V3" s="3" t="s">
+      <c r="V3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="W3" s="3" t="s">
+      <c r="W3" s="4" t="s">
         <v>20</v>
       </c>
       <c r="X3" s="4" t="s">
@@ -1439,74 +1608,116 @@
       <c r="AA3" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="AB3" s="4"/>
-      <c r="AC3" s="2"/>
-      <c r="AD3" s="2"/>
+      <c r="AB3" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC3" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="AD3" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE3" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="AF3" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="AG3" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="AH3" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="AI3" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="AJ3" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="AK3" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="AL3" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="AM3" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN3" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="AO3" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="AP3" s="6"/>
+      <c r="AQ3" s="2"/>
+      <c r="AR3" s="2"/>
     </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:30">
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:44">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
-      <c r="C4" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F4" s="3" t="s">
+      <c r="C4" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I4" s="3" t="s">
+      <c r="H4" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="I4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="J4" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="K4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="L4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="M4" s="3" t="s">
+      <c r="M4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="N4" s="3" t="s">
+      <c r="N4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="O4" s="3" t="s">
+      <c r="O4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="P4" s="3" t="s">
+      <c r="P4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="Q4" s="3" t="s">
+      <c r="Q4" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="R4" s="3" t="s">
+      <c r="R4" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="S4" s="3" t="s">
+      <c r="S4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="T4" s="3" t="s">
+      <c r="T4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="U4" s="3" t="s">
+      <c r="U4" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="V4" s="3" t="s">
+      <c r="V4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="W4" s="3" t="s">
+      <c r="W4" s="4" t="s">
         <v>20</v>
       </c>
       <c r="X4" s="4" t="s">
@@ -1518,92 +1729,176 @@
       <c r="Z4" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="AA4" s="4"/>
-      <c r="AB4" s="4"/>
-      <c r="AC4" s="2"/>
-      <c r="AD4" s="2"/>
+      <c r="AA4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB4" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC4" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="AD4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="AF4" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="AG4" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="AH4" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="AI4" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="AJ4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="AK4" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="AL4" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="AM4" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN4" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="AO4" s="6"/>
+      <c r="AP4" s="6"/>
+      <c r="AQ4" s="2"/>
+      <c r="AR4" s="2"/>
     </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:30">
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:44">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
-      <c r="C5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="N5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="P5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="R5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="S5" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="T5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="U5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="V5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="W5" s="3" t="s">
-        <v>26</v>
+      <c r="C5" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="M5" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="O5" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="P5" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q5" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="R5" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="S5" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="T5" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="U5" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="V5" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="W5" s="4" t="s">
+        <v>42</v>
       </c>
       <c r="X5" s="4" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="Y5" s="4" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="Z5" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="AA5" s="4"/>
-      <c r="AB5" s="4"/>
-      <c r="AC5" s="2"/>
-      <c r="AD5" s="2"/>
+        <v>40</v>
+      </c>
+      <c r="AA5" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="AB5" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="AC5" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="AD5" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="AE5" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF5" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="AG5" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH5" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="AI5" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AJ5" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="AK5" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="AL5" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="AM5" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="AN5" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="AO5" s="6"/>
+      <c r="AP5" s="6"/>
+      <c r="AQ5" s="2"/>
+      <c r="AR5" s="2"/>
     </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:27">
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:44">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1620,58 +1915,100 @@
         <v>1000</v>
       </c>
       <c r="H6" s="1">
+        <v>1.3</v>
+      </c>
+      <c r="I6" s="1">
         <v>5000</v>
-      </c>
-      <c r="I6" s="1">
-        <v>5000000</v>
       </c>
       <c r="J6" s="1">
         <v>1.3</v>
       </c>
       <c r="K6" s="1">
-        <v>5</v>
+        <v>5000000</v>
       </c>
       <c r="L6" s="1">
-        <v>5</v>
-      </c>
-      <c r="M6" s="1">
-        <v>5</v>
-      </c>
-      <c r="N6" s="1">
-        <v>5</v>
-      </c>
-      <c r="O6" s="1">
-        <v>5</v>
-      </c>
-      <c r="P6" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="1">
-        <v>0</v>
-      </c>
-      <c r="R6" s="1">
-        <v>0</v>
+        <v>1.3</v>
+      </c>
+      <c r="M6" s="7">
+        <v>0</v>
+      </c>
+      <c r="N6" s="7">
+        <v>0</v>
+      </c>
+      <c r="O6" s="7">
+        <v>0</v>
+      </c>
+      <c r="P6" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="7">
+        <v>0</v>
+      </c>
+      <c r="R6" s="7">
+        <v>0</v>
+      </c>
+      <c r="S6" s="1">
+        <v>5</v>
+      </c>
+      <c r="T6" s="1">
+        <v>5</v>
+      </c>
+      <c r="U6" s="1">
+        <v>5</v>
       </c>
       <c r="V6" s="1">
+        <v>5</v>
+      </c>
+      <c r="W6" s="1">
+        <v>5</v>
+      </c>
+      <c r="X6" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF6" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="1">
         <v>15</v>
       </c>
-      <c r="W6" s="1">
-        <v>5</v>
-      </c>
-      <c r="X6" s="1">
-        <v>5</v>
-      </c>
-      <c r="Y6" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z6" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA6" s="1" t="s">
-        <v>34</v>
+      <c r="AK6" s="1">
+        <v>5</v>
+      </c>
+      <c r="AL6" s="1">
+        <v>5</v>
+      </c>
+      <c r="AM6" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="AN6" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="AO6" s="1" t="s">
+        <v>48</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:27">
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:44">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -1688,58 +2025,100 @@
         <v>50000</v>
       </c>
       <c r="H7" s="1">
+        <v>1.3</v>
+      </c>
+      <c r="I7" s="1">
         <v>40000</v>
-      </c>
-      <c r="I7" s="1">
-        <v>50000000</v>
       </c>
       <c r="J7" s="1">
         <v>1.3</v>
       </c>
       <c r="K7" s="1">
-        <v>5</v>
+        <v>50000000</v>
       </c>
       <c r="L7" s="1">
-        <v>5</v>
-      </c>
-      <c r="M7" s="1">
-        <v>5</v>
-      </c>
-      <c r="N7" s="1">
-        <v>5</v>
-      </c>
-      <c r="O7" s="1">
-        <v>5</v>
-      </c>
-      <c r="P7" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="1">
-        <v>0</v>
-      </c>
-      <c r="R7" s="1">
-        <v>0</v>
+        <v>1.3</v>
+      </c>
+      <c r="M7" s="7">
+        <v>0</v>
+      </c>
+      <c r="N7" s="7">
+        <v>0</v>
+      </c>
+      <c r="O7" s="7">
+        <v>0</v>
+      </c>
+      <c r="P7" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="7">
+        <v>0</v>
+      </c>
+      <c r="R7" s="7">
+        <v>0</v>
+      </c>
+      <c r="S7" s="1">
+        <v>5</v>
+      </c>
+      <c r="T7" s="1">
+        <v>5</v>
+      </c>
+      <c r="U7" s="1">
+        <v>5</v>
       </c>
       <c r="V7" s="1">
+        <v>5</v>
+      </c>
+      <c r="W7" s="1">
+        <v>5</v>
+      </c>
+      <c r="X7" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH7" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI7" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="1">
         <v>14</v>
       </c>
-      <c r="W7" s="1">
-        <v>5</v>
-      </c>
-      <c r="X7" s="1">
-        <v>5</v>
-      </c>
-      <c r="Y7" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z7" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="AA7" s="1" t="s">
-        <v>36</v>
+      <c r="AK7" s="1">
+        <v>5</v>
+      </c>
+      <c r="AL7" s="1">
+        <v>5</v>
+      </c>
+      <c r="AM7" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="AN7" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="AO7" s="1" t="s">
+        <v>50</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:27">
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:44">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1756,58 +2135,100 @@
         <v>40000</v>
       </c>
       <c r="H8" s="1">
+        <v>1.3</v>
+      </c>
+      <c r="I8" s="1">
         <v>80000</v>
-      </c>
-      <c r="I8" s="1">
-        <v>50000000</v>
       </c>
       <c r="J8" s="1">
         <v>1.3</v>
       </c>
       <c r="K8" s="1">
-        <v>5</v>
+        <v>50000000</v>
       </c>
       <c r="L8" s="1">
-        <v>5</v>
-      </c>
-      <c r="M8" s="1">
-        <v>5</v>
-      </c>
-      <c r="N8" s="1">
-        <v>5</v>
-      </c>
-      <c r="O8" s="1">
-        <v>5</v>
-      </c>
-      <c r="P8" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="1">
-        <v>0</v>
-      </c>
-      <c r="R8" s="1">
-        <v>0</v>
+        <v>1.3</v>
+      </c>
+      <c r="M8" s="7">
+        <v>0</v>
+      </c>
+      <c r="N8" s="7">
+        <v>0</v>
+      </c>
+      <c r="O8" s="7">
+        <v>0</v>
+      </c>
+      <c r="P8" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="7">
+        <v>0</v>
+      </c>
+      <c r="R8" s="7">
+        <v>0</v>
+      </c>
+      <c r="S8" s="1">
+        <v>5</v>
+      </c>
+      <c r="T8" s="1">
+        <v>5</v>
+      </c>
+      <c r="U8" s="1">
+        <v>5</v>
       </c>
       <c r="V8" s="1">
+        <v>5</v>
+      </c>
+      <c r="W8" s="1">
+        <v>5</v>
+      </c>
+      <c r="X8" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ8" s="1">
         <v>16</v>
       </c>
-      <c r="W8" s="1">
-        <v>5</v>
-      </c>
-      <c r="X8" s="1">
-        <v>5</v>
-      </c>
-      <c r="Y8" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="Z8" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="AA8" s="1" t="s">
-        <v>39</v>
+      <c r="AK8" s="1">
+        <v>5</v>
+      </c>
+      <c r="AL8" s="1">
+        <v>5</v>
+      </c>
+      <c r="AM8" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="AN8" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="AO8" s="1" t="s">
+        <v>53</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:27">
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:44">
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -1824,58 +2245,100 @@
         <v>100000</v>
       </c>
       <c r="H9" s="1">
+        <v>1.3</v>
+      </c>
+      <c r="I9" s="1">
         <v>20000</v>
-      </c>
-      <c r="I9" s="1">
-        <v>100000000</v>
       </c>
       <c r="J9" s="1">
         <v>1.3</v>
       </c>
       <c r="K9" s="1">
-        <v>5</v>
+        <v>100000000</v>
       </c>
       <c r="L9" s="1">
-        <v>5</v>
-      </c>
-      <c r="M9" s="1">
-        <v>5</v>
-      </c>
-      <c r="N9" s="1">
-        <v>5</v>
-      </c>
-      <c r="O9" s="1">
-        <v>5</v>
-      </c>
-      <c r="P9" s="1">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="1">
-        <v>0</v>
-      </c>
-      <c r="R9" s="1">
-        <v>0</v>
+        <v>1.3</v>
+      </c>
+      <c r="M9" s="7">
+        <v>0</v>
+      </c>
+      <c r="N9" s="7">
+        <v>0</v>
+      </c>
+      <c r="O9" s="7">
+        <v>0</v>
+      </c>
+      <c r="P9" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="7">
+        <v>0</v>
+      </c>
+      <c r="R9" s="7">
+        <v>0</v>
+      </c>
+      <c r="S9" s="1">
+        <v>5</v>
+      </c>
+      <c r="T9" s="1">
+        <v>5</v>
+      </c>
+      <c r="U9" s="1">
+        <v>5</v>
       </c>
       <c r="V9" s="1">
+        <v>5</v>
+      </c>
+      <c r="W9" s="1">
+        <v>5</v>
+      </c>
+      <c r="X9" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y9" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH9" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI9" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ9" s="1">
         <v>26</v>
       </c>
-      <c r="W9" s="1">
-        <v>5</v>
-      </c>
-      <c r="X9" s="1">
-        <v>5</v>
-      </c>
-      <c r="Y9" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="Z9" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="AA9" s="1" t="s">
-        <v>41</v>
+      <c r="AK9" s="1">
+        <v>5</v>
+      </c>
+      <c r="AL9" s="1">
+        <v>5</v>
+      </c>
+      <c r="AM9" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="AN9" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="AO9" s="1" t="s">
+        <v>55</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:27">
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:44">
       <c r="C10" s="1">
         <v>5</v>
       </c>
@@ -1892,58 +2355,100 @@
         <v>100000</v>
       </c>
       <c r="H10" s="1">
+        <v>1.3</v>
+      </c>
+      <c r="I10" s="1">
         <v>20000</v>
-      </c>
-      <c r="I10" s="1">
-        <v>100000000</v>
       </c>
       <c r="J10" s="1">
         <v>1.3</v>
       </c>
       <c r="K10" s="1">
-        <v>5</v>
+        <v>100000000</v>
       </c>
       <c r="L10" s="1">
-        <v>5</v>
-      </c>
-      <c r="M10" s="1">
-        <v>5</v>
-      </c>
-      <c r="N10" s="1">
-        <v>5</v>
-      </c>
-      <c r="O10" s="1">
-        <v>5</v>
-      </c>
-      <c r="P10" s="1">
-        <v>2</v>
-      </c>
-      <c r="Q10" s="1">
-        <v>0</v>
-      </c>
-      <c r="R10" s="1">
-        <v>0</v>
+        <v>1.3</v>
+      </c>
+      <c r="M10" s="7">
+        <v>0</v>
+      </c>
+      <c r="N10" s="7">
+        <v>0</v>
+      </c>
+      <c r="O10" s="7">
+        <v>0</v>
+      </c>
+      <c r="P10" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="7">
+        <v>0</v>
+      </c>
+      <c r="R10" s="7">
+        <v>0</v>
+      </c>
+      <c r="S10" s="1">
+        <v>5</v>
+      </c>
+      <c r="T10" s="1">
+        <v>5</v>
+      </c>
+      <c r="U10" s="1">
+        <v>5</v>
       </c>
       <c r="V10" s="1">
+        <v>5</v>
+      </c>
+      <c r="W10" s="1">
+        <v>5</v>
+      </c>
+      <c r="X10" s="1">
+        <v>2</v>
+      </c>
+      <c r="Y10" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ10" s="1">
         <v>27</v>
       </c>
-      <c r="W10" s="1">
-        <v>5</v>
-      </c>
-      <c r="X10" s="1">
-        <v>5</v>
-      </c>
-      <c r="Y10" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z10" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="AA10" s="1" t="s">
-        <v>41</v>
+      <c r="AK10" s="1">
+        <v>5</v>
+      </c>
+      <c r="AL10" s="1">
+        <v>5</v>
+      </c>
+      <c r="AM10" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="AN10" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="AO10" s="1" t="s">
+        <v>55</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:27">
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="1:44">
       <c r="C11" s="1">
         <v>6</v>
       </c>
@@ -1960,58 +2465,100 @@
         <v>100000</v>
       </c>
       <c r="H11" s="1">
+        <v>1.3</v>
+      </c>
+      <c r="I11" s="1">
         <v>20000</v>
-      </c>
-      <c r="I11" s="1">
-        <v>100000000</v>
       </c>
       <c r="J11" s="1">
         <v>1.3</v>
       </c>
       <c r="K11" s="1">
-        <v>5</v>
+        <v>100000000</v>
       </c>
       <c r="L11" s="1">
-        <v>5</v>
-      </c>
-      <c r="M11" s="1">
-        <v>5</v>
-      </c>
-      <c r="N11" s="1">
-        <v>5</v>
-      </c>
-      <c r="O11" s="1">
-        <v>5</v>
-      </c>
-      <c r="P11" s="1">
+        <v>1.3</v>
+      </c>
+      <c r="M11" s="7">
+        <v>0</v>
+      </c>
+      <c r="N11" s="7">
+        <v>0</v>
+      </c>
+      <c r="O11" s="7">
+        <v>0</v>
+      </c>
+      <c r="P11" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="7">
+        <v>0</v>
+      </c>
+      <c r="R11" s="7">
+        <v>0</v>
+      </c>
+      <c r="S11" s="1">
+        <v>5</v>
+      </c>
+      <c r="T11" s="1">
+        <v>5</v>
+      </c>
+      <c r="U11" s="1">
+        <v>5</v>
+      </c>
+      <c r="V11" s="1">
+        <v>5</v>
+      </c>
+      <c r="W11" s="1">
+        <v>5</v>
+      </c>
+      <c r="X11" s="1">
         <v>3</v>
       </c>
-      <c r="Q11" s="1">
-        <v>0</v>
-      </c>
-      <c r="R11" s="1">
-        <v>0</v>
-      </c>
-      <c r="V11" s="1">
+      <c r="Y11" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF11" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG11" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH11" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI11" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ11" s="1">
         <v>28</v>
       </c>
-      <c r="W11" s="1">
-        <v>5</v>
-      </c>
-      <c r="X11" s="1">
-        <v>5</v>
-      </c>
-      <c r="Y11" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="Z11" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="AA11" s="1" t="s">
-        <v>41</v>
+      <c r="AK11" s="1">
+        <v>5</v>
+      </c>
+      <c r="AL11" s="1">
+        <v>5</v>
+      </c>
+      <c r="AM11" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="AN11" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="AO11" s="1" t="s">
+        <v>55</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:27">
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="1:44">
       <c r="C12" s="1">
         <v>7</v>
       </c>
@@ -2024,71 +2571,113 @@
       <c r="F12" s="1">
         <v>2000</v>
       </c>
-      <c r="G12" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>46</v>
+      <c r="G12" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="H12" s="1">
+        <v>1.6</v>
+      </c>
+      <c r="I12" s="12" t="s">
+        <v>59</v>
       </c>
       <c r="J12" s="1">
         <v>1.6</v>
       </c>
-      <c r="K12" s="1">
-        <v>2</v>
+      <c r="K12" s="12" t="s">
+        <v>60</v>
       </c>
       <c r="L12" s="1">
-        <v>5</v>
-      </c>
-      <c r="M12" s="1">
-        <v>5</v>
-      </c>
-      <c r="N12" s="1">
-        <v>5</v>
-      </c>
-      <c r="O12" s="1">
-        <v>5</v>
-      </c>
-      <c r="P12" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="1">
-        <v>0</v>
-      </c>
-      <c r="R12" s="1">
-        <v>0</v>
-      </c>
-      <c r="S12" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="T12" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="U12" s="6" t="s">
-        <v>48</v>
+        <v>1.6</v>
+      </c>
+      <c r="M12" s="7">
+        <v>0</v>
+      </c>
+      <c r="N12" s="7">
+        <v>0</v>
+      </c>
+      <c r="O12" s="7">
+        <v>0</v>
+      </c>
+      <c r="P12" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="7">
+        <v>0</v>
+      </c>
+      <c r="R12" s="7">
+        <v>0</v>
+      </c>
+      <c r="S12" s="1">
+        <v>2</v>
+      </c>
+      <c r="T12" s="1">
+        <v>5</v>
+      </c>
+      <c r="U12" s="1">
+        <v>5</v>
       </c>
       <c r="V12" s="1">
+        <v>5</v>
+      </c>
+      <c r="W12" s="1">
+        <v>5</v>
+      </c>
+      <c r="X12" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB12" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="AC12" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="AD12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ12" s="1">
         <v>2001</v>
       </c>
-      <c r="W12" s="1">
-        <v>1</v>
-      </c>
-      <c r="X12" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y12" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="Z12" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="AA12" s="1" t="s">
-        <v>50</v>
+      <c r="AK12" s="1">
+        <v>1</v>
+      </c>
+      <c r="AL12" s="1">
+        <v>1</v>
+      </c>
+      <c r="AM12" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="AN12" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="AO12" s="1" t="s">
+        <v>64</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:27">
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="1:44">
       <c r="C13" s="1">
         <v>8</v>
       </c>
@@ -2101,71 +2690,113 @@
       <c r="F13" s="1">
         <v>2000</v>
       </c>
-      <c r="G13" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="I13" s="6" t="s">
-        <v>52</v>
+      <c r="G13" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="H13" s="1">
+        <v>1.6</v>
+      </c>
+      <c r="I13" s="12" t="s">
+        <v>65</v>
       </c>
       <c r="J13" s="1">
         <v>1.6</v>
       </c>
-      <c r="K13" s="1">
-        <v>2</v>
+      <c r="K13" s="12" t="s">
+        <v>66</v>
       </c>
       <c r="L13" s="1">
-        <v>5</v>
-      </c>
-      <c r="M13" s="1">
-        <v>5</v>
-      </c>
-      <c r="N13" s="1">
-        <v>5</v>
-      </c>
-      <c r="O13" s="1">
-        <v>5</v>
-      </c>
-      <c r="P13" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="1">
-        <v>0</v>
-      </c>
-      <c r="R13" s="1">
-        <v>0</v>
-      </c>
-      <c r="S13" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="T13" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="U13" s="6" t="s">
-        <v>55</v>
+        <v>1.6</v>
+      </c>
+      <c r="M13" s="7">
+        <v>0</v>
+      </c>
+      <c r="N13" s="7">
+        <v>0</v>
+      </c>
+      <c r="O13" s="7">
+        <v>0</v>
+      </c>
+      <c r="P13" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="7">
+        <v>0</v>
+      </c>
+      <c r="R13" s="7">
+        <v>0</v>
+      </c>
+      <c r="S13" s="1">
+        <v>2</v>
+      </c>
+      <c r="T13" s="1">
+        <v>5</v>
+      </c>
+      <c r="U13" s="1">
+        <v>5</v>
       </c>
       <c r="V13" s="1">
+        <v>5</v>
+      </c>
+      <c r="W13" s="1">
+        <v>5</v>
+      </c>
+      <c r="X13" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB13" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="AC13" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="1">
         <v>2002</v>
       </c>
-      <c r="W13" s="1">
-        <v>1</v>
-      </c>
-      <c r="X13" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y13" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="Z13" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="AA13" s="1" t="s">
-        <v>57</v>
+      <c r="AK13" s="1">
+        <v>1</v>
+      </c>
+      <c r="AL13" s="1">
+        <v>1</v>
+      </c>
+      <c r="AM13" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="AN13" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="AO13" s="1" t="s">
+        <v>71</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:27">
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="1:44">
       <c r="C14" s="1">
         <v>9</v>
       </c>
@@ -2178,71 +2809,113 @@
       <c r="F14" s="1">
         <v>2000</v>
       </c>
-      <c r="G14" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>58</v>
+      <c r="G14" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="H14" s="1">
+        <v>1.6</v>
+      </c>
+      <c r="I14" s="12" t="s">
+        <v>59</v>
       </c>
       <c r="J14" s="1">
         <v>1.6</v>
       </c>
-      <c r="K14" s="1">
-        <v>2</v>
+      <c r="K14" s="12" t="s">
+        <v>72</v>
       </c>
       <c r="L14" s="1">
-        <v>5</v>
-      </c>
-      <c r="M14" s="1">
-        <v>5</v>
-      </c>
-      <c r="N14" s="1">
-        <v>5</v>
-      </c>
-      <c r="O14" s="1">
-        <v>5</v>
-      </c>
-      <c r="P14" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="1">
-        <v>0</v>
-      </c>
-      <c r="R14" s="1">
-        <v>0</v>
-      </c>
-      <c r="S14" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="T14" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="U14" s="6" t="s">
-        <v>61</v>
+        <v>1.6</v>
+      </c>
+      <c r="M14" s="7">
+        <v>0</v>
+      </c>
+      <c r="N14" s="7">
+        <v>0</v>
+      </c>
+      <c r="O14" s="7">
+        <v>0</v>
+      </c>
+      <c r="P14" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="7">
+        <v>0</v>
+      </c>
+      <c r="R14" s="7">
+        <v>0</v>
+      </c>
+      <c r="S14" s="1">
+        <v>2</v>
+      </c>
+      <c r="T14" s="1">
+        <v>5</v>
+      </c>
+      <c r="U14" s="1">
+        <v>5</v>
       </c>
       <c r="V14" s="1">
+        <v>5</v>
+      </c>
+      <c r="W14" s="1">
+        <v>5</v>
+      </c>
+      <c r="X14" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="AB14" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC14" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="1">
         <v>2003</v>
       </c>
-      <c r="W14" s="1">
-        <v>1</v>
-      </c>
-      <c r="X14" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y14" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="Z14" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="AA14" s="1" t="s">
-        <v>63</v>
+      <c r="AK14" s="1">
+        <v>1</v>
+      </c>
+      <c r="AL14" s="1">
+        <v>1</v>
+      </c>
+      <c r="AM14" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="AN14" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="AO14" s="1" t="s">
+        <v>77</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:27">
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="1:44">
       <c r="C15" s="1">
         <v>10</v>
       </c>
@@ -2255,62 +2928,104 @@
       <c r="F15" s="1">
         <v>2000</v>
       </c>
-      <c r="G15" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="I15" s="6" t="s">
-        <v>58</v>
+      <c r="G15" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="H15" s="1">
+        <v>1.3</v>
+      </c>
+      <c r="I15" s="12" t="s">
+        <v>59</v>
       </c>
       <c r="J15" s="1">
         <v>1.3</v>
       </c>
-      <c r="K15" s="1">
-        <v>2</v>
+      <c r="K15" s="12" t="s">
+        <v>72</v>
       </c>
       <c r="L15" s="1">
-        <v>5</v>
-      </c>
-      <c r="M15" s="1">
-        <v>5</v>
-      </c>
-      <c r="N15" s="1">
-        <v>5</v>
-      </c>
-      <c r="O15" s="1">
-        <v>5</v>
-      </c>
-      <c r="P15" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="5">
+        <v>1.3</v>
+      </c>
+      <c r="M15" s="7">
+        <v>0</v>
+      </c>
+      <c r="N15" s="7">
+        <v>0</v>
+      </c>
+      <c r="O15" s="7">
+        <v>0</v>
+      </c>
+      <c r="P15" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="7">
+        <v>0</v>
+      </c>
+      <c r="R15" s="7">
+        <v>0</v>
+      </c>
+      <c r="S15" s="1">
+        <v>2</v>
+      </c>
+      <c r="T15" s="1">
+        <v>5</v>
+      </c>
+      <c r="U15" s="1">
+        <v>5</v>
+      </c>
+      <c r="V15" s="1">
+        <v>5</v>
+      </c>
+      <c r="W15" s="1">
+        <v>5</v>
+      </c>
+      <c r="X15" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="8">
         <v>18</v>
       </c>
-      <c r="R15" s="1">
+      <c r="Z15" s="1">
         <v>100</v>
       </c>
-      <c r="V15" s="5">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ15" s="8">
         <v>18</v>
       </c>
-      <c r="W15" s="1">
+      <c r="AK15" s="1">
         <v>10</v>
       </c>
-      <c r="X15" s="1">
+      <c r="AL15" s="1">
         <v>10</v>
       </c>
-      <c r="Y15" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="Z15" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="AA15" s="1" t="s">
-        <v>64</v>
+      <c r="AM15" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="AN15" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="AO15" s="1" t="s">
+        <v>78</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:27">
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="1:44">
       <c r="C16" s="1">
         <v>11</v>
       </c>
@@ -2323,62 +3038,104 @@
       <c r="F16" s="1">
         <v>2000</v>
       </c>
-      <c r="G16" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="I16" s="6" t="s">
-        <v>58</v>
+      <c r="G16" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="H16" s="1">
+        <v>1.3</v>
+      </c>
+      <c r="I16" s="12" t="s">
+        <v>59</v>
       </c>
       <c r="J16" s="1">
         <v>1.3</v>
       </c>
-      <c r="K16" s="1">
-        <v>2</v>
+      <c r="K16" s="12" t="s">
+        <v>72</v>
       </c>
       <c r="L16" s="1">
-        <v>5</v>
-      </c>
-      <c r="M16" s="1">
-        <v>5</v>
-      </c>
-      <c r="N16" s="1">
-        <v>5</v>
-      </c>
-      <c r="O16" s="1">
-        <v>5</v>
-      </c>
-      <c r="P16" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="5">
+        <v>1.3</v>
+      </c>
+      <c r="M16" s="7">
+        <v>0</v>
+      </c>
+      <c r="N16" s="7">
+        <v>0</v>
+      </c>
+      <c r="O16" s="7">
+        <v>0</v>
+      </c>
+      <c r="P16" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="7">
+        <v>0</v>
+      </c>
+      <c r="R16" s="7">
+        <v>0</v>
+      </c>
+      <c r="S16" s="1">
+        <v>2</v>
+      </c>
+      <c r="T16" s="1">
+        <v>5</v>
+      </c>
+      <c r="U16" s="1">
+        <v>5</v>
+      </c>
+      <c r="V16" s="1">
+        <v>5</v>
+      </c>
+      <c r="W16" s="1">
+        <v>5</v>
+      </c>
+      <c r="X16" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="8">
         <v>19</v>
       </c>
-      <c r="R16" s="1">
+      <c r="Z16" s="1">
         <v>100</v>
       </c>
-      <c r="V16" s="5">
+      <c r="AD16" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE16" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF16" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG16" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH16" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI16" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ16" s="8">
         <v>19</v>
       </c>
-      <c r="W16" s="1">
+      <c r="AK16" s="1">
         <v>10</v>
       </c>
-      <c r="X16" s="1">
+      <c r="AL16" s="1">
         <v>10</v>
       </c>
-      <c r="Y16" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="Z16" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="AA16" s="1" t="s">
-        <v>65</v>
+      <c r="AM16" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="AN16" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="AO16" s="1" t="s">
+        <v>79</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:27">
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:41">
       <c r="C17" s="1">
         <v>12</v>
       </c>
@@ -2391,62 +3148,104 @@
       <c r="F17" s="1">
         <v>2000</v>
       </c>
-      <c r="G17" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="H17" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="I17" s="6" t="s">
-        <v>58</v>
+      <c r="G17" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="H17" s="1">
+        <v>1.3</v>
+      </c>
+      <c r="I17" s="12" t="s">
+        <v>59</v>
       </c>
       <c r="J17" s="1">
         <v>1.3</v>
       </c>
-      <c r="K17" s="1">
-        <v>2</v>
+      <c r="K17" s="12" t="s">
+        <v>72</v>
       </c>
       <c r="L17" s="1">
-        <v>5</v>
-      </c>
-      <c r="M17" s="1">
-        <v>5</v>
-      </c>
-      <c r="N17" s="1">
-        <v>5</v>
-      </c>
-      <c r="O17" s="1">
-        <v>5</v>
-      </c>
-      <c r="P17" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="5">
+        <v>1.3</v>
+      </c>
+      <c r="M17" s="7">
+        <v>0</v>
+      </c>
+      <c r="N17" s="7">
+        <v>0</v>
+      </c>
+      <c r="O17" s="7">
+        <v>0</v>
+      </c>
+      <c r="P17" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="7">
+        <v>0</v>
+      </c>
+      <c r="R17" s="7">
+        <v>0</v>
+      </c>
+      <c r="S17" s="1">
+        <v>2</v>
+      </c>
+      <c r="T17" s="1">
+        <v>5</v>
+      </c>
+      <c r="U17" s="1">
+        <v>5</v>
+      </c>
+      <c r="V17" s="1">
+        <v>5</v>
+      </c>
+      <c r="W17" s="1">
+        <v>5</v>
+      </c>
+      <c r="X17" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="8">
         <v>20</v>
       </c>
-      <c r="R17" s="1">
+      <c r="Z17" s="1">
         <v>100</v>
       </c>
-      <c r="V17" s="5">
+      <c r="AD17" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE17" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF17" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG17" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH17" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI17" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ17" s="8">
         <v>20</v>
       </c>
-      <c r="W17" s="1">
+      <c r="AK17" s="1">
         <v>10</v>
       </c>
-      <c r="X17" s="1">
+      <c r="AL17" s="1">
         <v>10</v>
       </c>
-      <c r="Y17" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="Z17" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="AA17" s="1" t="s">
-        <v>66</v>
+      <c r="AM17" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="AN17" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="AO17" s="1" t="s">
+        <v>80</v>
       </c>
     </row>
-    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:27">
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:41">
       <c r="C18" s="1">
         <v>13</v>
       </c>
@@ -2459,62 +3258,104 @@
       <c r="F18" s="1">
         <v>2000</v>
       </c>
-      <c r="G18" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="I18" s="6" t="s">
-        <v>58</v>
+      <c r="G18" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="H18" s="1">
+        <v>1.3</v>
+      </c>
+      <c r="I18" s="12" t="s">
+        <v>59</v>
       </c>
       <c r="J18" s="1">
         <v>1.3</v>
       </c>
-      <c r="K18" s="1">
-        <v>2</v>
+      <c r="K18" s="12" t="s">
+        <v>72</v>
       </c>
       <c r="L18" s="1">
-        <v>5</v>
-      </c>
-      <c r="M18" s="1">
-        <v>5</v>
-      </c>
-      <c r="N18" s="1">
-        <v>5</v>
-      </c>
-      <c r="O18" s="1">
-        <v>5</v>
-      </c>
-      <c r="P18" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="5">
+        <v>1.3</v>
+      </c>
+      <c r="M18" s="7">
+        <v>0</v>
+      </c>
+      <c r="N18" s="7">
+        <v>0</v>
+      </c>
+      <c r="O18" s="7">
+        <v>0</v>
+      </c>
+      <c r="P18" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="7">
+        <v>0</v>
+      </c>
+      <c r="R18" s="7">
+        <v>0</v>
+      </c>
+      <c r="S18" s="1">
+        <v>2</v>
+      </c>
+      <c r="T18" s="1">
+        <v>5</v>
+      </c>
+      <c r="U18" s="1">
+        <v>5</v>
+      </c>
+      <c r="V18" s="1">
+        <v>5</v>
+      </c>
+      <c r="W18" s="1">
+        <v>5</v>
+      </c>
+      <c r="X18" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="8">
         <v>24</v>
       </c>
-      <c r="R18" s="1">
+      <c r="Z18" s="1">
         <v>100</v>
       </c>
-      <c r="V18" s="5">
+      <c r="AD18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ18" s="8">
         <v>24</v>
       </c>
-      <c r="W18" s="1">
+      <c r="AK18" s="1">
         <v>10</v>
       </c>
-      <c r="X18" s="1">
+      <c r="AL18" s="1">
         <v>10</v>
       </c>
-      <c r="Y18" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="Z18" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="AA18" s="1" t="s">
-        <v>67</v>
+      <c r="AM18" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="AN18" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="AO18" s="1" t="s">
+        <v>81</v>
       </c>
     </row>
-    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:27">
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:41">
       <c r="C19" s="1">
         <v>14</v>
       </c>
@@ -2527,62 +3368,104 @@
       <c r="F19" s="1">
         <v>2000</v>
       </c>
-      <c r="G19" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="H19" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="I19" s="6" t="s">
-        <v>69</v>
+      <c r="G19" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="H19" s="1">
+        <v>1.3</v>
+      </c>
+      <c r="I19" s="12" t="s">
+        <v>60</v>
       </c>
       <c r="J19" s="1">
         <v>1.3</v>
       </c>
-      <c r="K19" s="1">
-        <v>2</v>
+      <c r="K19" s="12" t="s">
+        <v>83</v>
       </c>
       <c r="L19" s="1">
-        <v>5</v>
-      </c>
-      <c r="M19" s="1">
-        <v>5</v>
-      </c>
-      <c r="N19" s="1">
-        <v>5</v>
-      </c>
-      <c r="O19" s="1">
-        <v>5</v>
-      </c>
-      <c r="P19" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="5">
+        <v>1.3</v>
+      </c>
+      <c r="M19" s="7">
+        <v>0</v>
+      </c>
+      <c r="N19" s="7">
+        <v>0</v>
+      </c>
+      <c r="O19" s="7">
+        <v>0</v>
+      </c>
+      <c r="P19" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="7">
+        <v>0</v>
+      </c>
+      <c r="R19" s="7">
+        <v>0</v>
+      </c>
+      <c r="S19" s="1">
+        <v>2</v>
+      </c>
+      <c r="T19" s="1">
+        <v>5</v>
+      </c>
+      <c r="U19" s="1">
+        <v>5</v>
+      </c>
+      <c r="V19" s="1">
+        <v>5</v>
+      </c>
+      <c r="W19" s="1">
+        <v>5</v>
+      </c>
+      <c r="X19" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="8">
         <v>7</v>
       </c>
-      <c r="R19" s="1">
+      <c r="Z19" s="1">
         <v>10</v>
       </c>
-      <c r="V19" s="5">
+      <c r="AD19" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE19" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF19" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG19" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH19" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI19" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ19" s="8">
         <v>7</v>
       </c>
-      <c r="W19" s="1">
-        <v>1</v>
-      </c>
-      <c r="X19" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y19" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="Z19" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="AA19" s="1" t="s">
-        <v>70</v>
+      <c r="AK19" s="1">
+        <v>1</v>
+      </c>
+      <c r="AL19" s="1">
+        <v>1</v>
+      </c>
+      <c r="AM19" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="AN19" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="AO19" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:27">
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:41">
       <c r="C20" s="1">
         <v>15</v>
       </c>
@@ -2595,62 +3478,104 @@
       <c r="F20" s="1">
         <v>2000</v>
       </c>
-      <c r="G20" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="I20" s="6" t="s">
-        <v>69</v>
+      <c r="G20" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="H20" s="1">
+        <v>1.3</v>
+      </c>
+      <c r="I20" s="12" t="s">
+        <v>60</v>
       </c>
       <c r="J20" s="1">
         <v>1.3</v>
       </c>
-      <c r="K20" s="1">
-        <v>2</v>
+      <c r="K20" s="12" t="s">
+        <v>83</v>
       </c>
       <c r="L20" s="1">
-        <v>5</v>
-      </c>
-      <c r="M20" s="1">
-        <v>5</v>
-      </c>
-      <c r="N20" s="1">
-        <v>5</v>
-      </c>
-      <c r="O20" s="1">
-        <v>5</v>
-      </c>
-      <c r="P20" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="5">
+        <v>1.3</v>
+      </c>
+      <c r="M20" s="7">
+        <v>0</v>
+      </c>
+      <c r="N20" s="7">
+        <v>0</v>
+      </c>
+      <c r="O20" s="7">
+        <v>0</v>
+      </c>
+      <c r="P20" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="7">
+        <v>0</v>
+      </c>
+      <c r="R20" s="7">
+        <v>0</v>
+      </c>
+      <c r="S20" s="1">
+        <v>2</v>
+      </c>
+      <c r="T20" s="1">
+        <v>5</v>
+      </c>
+      <c r="U20" s="1">
+        <v>5</v>
+      </c>
+      <c r="V20" s="1">
+        <v>5</v>
+      </c>
+      <c r="W20" s="1">
+        <v>5</v>
+      </c>
+      <c r="X20" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="8">
         <v>9</v>
       </c>
-      <c r="R20" s="1">
+      <c r="Z20" s="1">
         <v>10</v>
       </c>
-      <c r="V20" s="5">
+      <c r="AD20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ20" s="8">
         <v>9</v>
       </c>
-      <c r="W20" s="1">
-        <v>1</v>
-      </c>
-      <c r="X20" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y20" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="Z20" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="AA20" s="1" t="s">
-        <v>71</v>
+      <c r="AK20" s="1">
+        <v>1</v>
+      </c>
+      <c r="AL20" s="1">
+        <v>1</v>
+      </c>
+      <c r="AM20" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="AN20" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="AO20" s="1" t="s">
+        <v>85</v>
       </c>
     </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:27">
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:41">
       <c r="C21" s="1">
         <v>16</v>
       </c>
@@ -2663,64 +3588,1200 @@
       <c r="F21" s="1">
         <v>2000</v>
       </c>
-      <c r="G21" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="H21" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="I21" s="6" t="s">
-        <v>69</v>
+      <c r="G21" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="H21" s="1">
+        <v>1.3</v>
+      </c>
+      <c r="I21" s="12" t="s">
+        <v>60</v>
       </c>
       <c r="J21" s="1">
         <v>1.3</v>
       </c>
-      <c r="K21" s="1">
-        <v>2</v>
+      <c r="K21" s="12" t="s">
+        <v>83</v>
       </c>
       <c r="L21" s="1">
-        <v>5</v>
-      </c>
-      <c r="M21" s="1">
-        <v>5</v>
-      </c>
-      <c r="N21" s="1">
-        <v>5</v>
-      </c>
-      <c r="O21" s="1">
-        <v>5</v>
-      </c>
-      <c r="P21" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="5">
+        <v>1.3</v>
+      </c>
+      <c r="M21" s="7">
+        <v>0</v>
+      </c>
+      <c r="N21" s="7">
+        <v>0</v>
+      </c>
+      <c r="O21" s="7">
+        <v>0</v>
+      </c>
+      <c r="P21" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="7">
+        <v>0</v>
+      </c>
+      <c r="R21" s="7">
+        <v>0</v>
+      </c>
+      <c r="S21" s="1">
+        <v>2</v>
+      </c>
+      <c r="T21" s="1">
+        <v>5</v>
+      </c>
+      <c r="U21" s="1">
+        <v>5</v>
+      </c>
+      <c r="V21" s="1">
+        <v>5</v>
+      </c>
+      <c r="W21" s="1">
+        <v>5</v>
+      </c>
+      <c r="X21" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="8">
         <v>12</v>
       </c>
-      <c r="R21" s="1">
+      <c r="Z21" s="1">
         <v>10</v>
       </c>
-      <c r="V21" s="5">
+      <c r="AD21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ21" s="8">
         <v>12</v>
       </c>
-      <c r="W21" s="1">
-        <v>1</v>
-      </c>
-      <c r="X21" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y21" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="Z21" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="AA21" s="1" t="s">
-        <v>72</v>
-      </c>
+      <c r="AK21" s="1">
+        <v>1</v>
+      </c>
+      <c r="AL21" s="1">
+        <v>1</v>
+      </c>
+      <c r="AM21" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="AN21" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="AO21" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="3:41">
+      <c r="C22" s="1">
+        <v>17</v>
+      </c>
+      <c r="D22" s="1">
+        <v>17</v>
+      </c>
+      <c r="E22" s="1">
+        <v>1</v>
+      </c>
+      <c r="F22" s="1">
+        <v>400</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="H22" s="2">
+        <v>2</v>
+      </c>
+      <c r="I22" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="J22" s="2">
+        <v>1</v>
+      </c>
+      <c r="K22" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="L22" s="2">
+        <v>2</v>
+      </c>
+      <c r="M22" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="N22" s="7">
+        <v>2</v>
+      </c>
+      <c r="O22" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="P22" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="Q22" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="R22" s="7">
+        <v>2</v>
+      </c>
+      <c r="S22" s="10">
+        <v>100000</v>
+      </c>
+      <c r="T22" s="10">
+        <v>100000</v>
+      </c>
+      <c r="U22" s="10">
+        <v>100000</v>
+      </c>
+      <c r="V22" s="10">
+        <v>100000</v>
+      </c>
+      <c r="W22" s="10">
+        <v>1000</v>
+      </c>
+      <c r="X22" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y22" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="10">
+        <v>250</v>
+      </c>
+      <c r="AE22" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="AF22" s="10">
+        <v>400</v>
+      </c>
+      <c r="AG22" s="10">
+        <v>1</v>
+      </c>
+      <c r="AH22" s="10">
+        <v>300</v>
+      </c>
+      <c r="AI22" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="AJ22" s="2">
+        <v>2004</v>
+      </c>
+      <c r="AK22" s="1">
+        <v>1</v>
+      </c>
+      <c r="AL22" s="1">
+        <v>1</v>
+      </c>
+      <c r="AM22" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="AN22" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="AO22" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="3:41">
+      <c r="C23" s="1">
+        <v>18</v>
+      </c>
+      <c r="D23" s="1">
+        <v>18</v>
+      </c>
+      <c r="E23" s="1">
+        <v>1</v>
+      </c>
+      <c r="F23" s="1">
+        <v>400</v>
+      </c>
+      <c r="G23" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="H23" s="2">
+        <v>2</v>
+      </c>
+      <c r="I23" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="J23" s="2">
+        <v>1</v>
+      </c>
+      <c r="K23" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="L23" s="2">
+        <v>2</v>
+      </c>
+      <c r="M23" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="N23" s="7">
+        <v>2</v>
+      </c>
+      <c r="O23" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="P23" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="Q23" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="R23" s="7">
+        <v>2</v>
+      </c>
+      <c r="S23" s="10">
+        <v>100000</v>
+      </c>
+      <c r="T23" s="10">
+        <v>100000</v>
+      </c>
+      <c r="U23" s="10">
+        <v>100000</v>
+      </c>
+      <c r="V23" s="10">
+        <v>100000</v>
+      </c>
+      <c r="W23" s="10">
+        <v>1000</v>
+      </c>
+      <c r="X23" s="1">
+        <v>2</v>
+      </c>
+      <c r="Y23" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB23" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC23" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD23" s="10">
+        <v>250</v>
+      </c>
+      <c r="AE23" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="AF23" s="10">
+        <v>400</v>
+      </c>
+      <c r="AG23" s="10">
+        <v>1</v>
+      </c>
+      <c r="AH23" s="10">
+        <v>300</v>
+      </c>
+      <c r="AI23" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="AJ23" s="2">
+        <v>2005</v>
+      </c>
+      <c r="AK23" s="1">
+        <v>1</v>
+      </c>
+      <c r="AL23" s="1">
+        <v>1</v>
+      </c>
+      <c r="AM23" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="AN23" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="AO23" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="3:41">
+      <c r="C24" s="1">
+        <v>19</v>
+      </c>
+      <c r="D24" s="1">
+        <v>19</v>
+      </c>
+      <c r="E24" s="1">
+        <v>1</v>
+      </c>
+      <c r="F24" s="1">
+        <v>400</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="H24" s="2">
+        <v>2</v>
+      </c>
+      <c r="I24" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="J24" s="2">
+        <v>1</v>
+      </c>
+      <c r="K24" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="L24" s="2">
+        <v>2</v>
+      </c>
+      <c r="M24" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="N24" s="7">
+        <v>2</v>
+      </c>
+      <c r="O24" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="P24" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="Q24" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="R24" s="7">
+        <v>2</v>
+      </c>
+      <c r="S24" s="10">
+        <v>100000</v>
+      </c>
+      <c r="T24" s="10">
+        <v>100000</v>
+      </c>
+      <c r="U24" s="10">
+        <v>100000</v>
+      </c>
+      <c r="V24" s="10">
+        <v>100000</v>
+      </c>
+      <c r="W24" s="10">
+        <v>1000</v>
+      </c>
+      <c r="X24" s="1">
+        <v>3</v>
+      </c>
+      <c r="Y24" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD24" s="10">
+        <v>250</v>
+      </c>
+      <c r="AE24" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="AF24" s="10">
+        <v>400</v>
+      </c>
+      <c r="AG24" s="10">
+        <v>1</v>
+      </c>
+      <c r="AH24" s="10">
+        <v>300</v>
+      </c>
+      <c r="AI24" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="AJ24" s="2">
+        <v>2006</v>
+      </c>
+      <c r="AK24" s="1">
+        <v>1</v>
+      </c>
+      <c r="AL24" s="1">
+        <v>1</v>
+      </c>
+      <c r="AM24" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="AN24" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="AO24" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="3:41">
+      <c r="C25" s="1">
+        <v>20</v>
+      </c>
+      <c r="D25" s="1">
+        <v>20</v>
+      </c>
+      <c r="E25" s="1">
+        <v>1</v>
+      </c>
+      <c r="F25" s="1">
+        <v>400</v>
+      </c>
+      <c r="G25" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="H25" s="2">
+        <v>2</v>
+      </c>
+      <c r="I25" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="J25" s="2">
+        <v>1</v>
+      </c>
+      <c r="K25" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="L25" s="2">
+        <v>2</v>
+      </c>
+      <c r="M25" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="N25" s="7">
+        <v>2</v>
+      </c>
+      <c r="O25" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="P25" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="Q25" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="R25" s="7">
+        <v>2</v>
+      </c>
+      <c r="S25" s="10">
+        <v>200000</v>
+      </c>
+      <c r="T25" s="10">
+        <v>200000</v>
+      </c>
+      <c r="U25" s="10">
+        <v>200000</v>
+      </c>
+      <c r="V25" s="10">
+        <v>200000</v>
+      </c>
+      <c r="W25" s="10">
+        <v>1000</v>
+      </c>
+      <c r="X25" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y25" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA25" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB25" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD25" s="10">
+        <v>250</v>
+      </c>
+      <c r="AE25" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="AF25" s="10">
+        <v>400</v>
+      </c>
+      <c r="AG25" s="10">
+        <v>1</v>
+      </c>
+      <c r="AH25" s="10">
+        <v>300</v>
+      </c>
+      <c r="AI25" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="AJ25" s="2">
+        <v>2007</v>
+      </c>
+      <c r="AK25" s="1">
+        <v>1</v>
+      </c>
+      <c r="AL25" s="1">
+        <v>1</v>
+      </c>
+      <c r="AM25" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="AN25" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="AO25" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="3:41">
+      <c r="C26" s="1">
+        <v>21</v>
+      </c>
+      <c r="D26" s="1">
+        <v>21</v>
+      </c>
+      <c r="E26" s="1">
+        <v>1</v>
+      </c>
+      <c r="F26" s="1">
+        <v>400</v>
+      </c>
+      <c r="G26" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="H26" s="2">
+        <v>2</v>
+      </c>
+      <c r="I26" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="J26" s="2">
+        <v>1</v>
+      </c>
+      <c r="K26" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="L26" s="2">
+        <v>2</v>
+      </c>
+      <c r="M26" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="N26" s="7">
+        <v>2</v>
+      </c>
+      <c r="O26" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="P26" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="Q26" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="R26" s="7">
+        <v>2</v>
+      </c>
+      <c r="S26" s="10">
+        <v>200000</v>
+      </c>
+      <c r="T26" s="10">
+        <v>200000</v>
+      </c>
+      <c r="U26" s="10">
+        <v>200000</v>
+      </c>
+      <c r="V26" s="10">
+        <v>200000</v>
+      </c>
+      <c r="W26" s="10">
+        <v>1000</v>
+      </c>
+      <c r="X26" s="1">
+        <v>2</v>
+      </c>
+      <c r="Y26" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z26" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA26" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB26" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC26" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD26" s="10">
+        <v>250</v>
+      </c>
+      <c r="AE26" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="AF26" s="10">
+        <v>400</v>
+      </c>
+      <c r="AG26" s="10">
+        <v>1</v>
+      </c>
+      <c r="AH26" s="10">
+        <v>300</v>
+      </c>
+      <c r="AI26" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="AJ26" s="2">
+        <v>2008</v>
+      </c>
+      <c r="AK26" s="1">
+        <v>1</v>
+      </c>
+      <c r="AL26" s="1">
+        <v>1</v>
+      </c>
+      <c r="AM26" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="AN26" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="AO26" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="3:41">
+      <c r="C27" s="1">
+        <v>22</v>
+      </c>
+      <c r="D27" s="1">
+        <v>22</v>
+      </c>
+      <c r="E27" s="1">
+        <v>1</v>
+      </c>
+      <c r="F27" s="1">
+        <v>400</v>
+      </c>
+      <c r="G27" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="H27" s="2">
+        <v>2</v>
+      </c>
+      <c r="I27" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="J27" s="2">
+        <v>1</v>
+      </c>
+      <c r="K27" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="L27" s="2">
+        <v>2</v>
+      </c>
+      <c r="M27" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="N27" s="7">
+        <v>2</v>
+      </c>
+      <c r="O27" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="P27" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="Q27" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="R27" s="7">
+        <v>2</v>
+      </c>
+      <c r="S27" s="10">
+        <v>200000</v>
+      </c>
+      <c r="T27" s="10">
+        <v>200000</v>
+      </c>
+      <c r="U27" s="10">
+        <v>200000</v>
+      </c>
+      <c r="V27" s="10">
+        <v>200000</v>
+      </c>
+      <c r="W27" s="10">
+        <v>1000</v>
+      </c>
+      <c r="X27" s="1">
+        <v>3</v>
+      </c>
+      <c r="Y27" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z27" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA27" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB27" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC27" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD27" s="10">
+        <v>250</v>
+      </c>
+      <c r="AE27" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="AF27" s="10">
+        <v>400</v>
+      </c>
+      <c r="AG27" s="10">
+        <v>1</v>
+      </c>
+      <c r="AH27" s="10">
+        <v>300</v>
+      </c>
+      <c r="AI27" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="AJ27" s="2">
+        <v>2009</v>
+      </c>
+      <c r="AK27" s="1">
+        <v>1</v>
+      </c>
+      <c r="AL27" s="1">
+        <v>1</v>
+      </c>
+      <c r="AM27" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="AN27" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="AO27" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="3:41">
+      <c r="C28" s="1">
+        <v>23</v>
+      </c>
+      <c r="D28" s="1">
+        <v>23</v>
+      </c>
+      <c r="E28" s="1">
+        <v>1</v>
+      </c>
+      <c r="F28" s="1">
+        <v>400</v>
+      </c>
+      <c r="G28" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="H28" s="2">
+        <v>2</v>
+      </c>
+      <c r="I28" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="J28" s="2">
+        <v>1</v>
+      </c>
+      <c r="K28" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="L28" s="2">
+        <v>2</v>
+      </c>
+      <c r="M28" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="N28" s="7">
+        <v>2</v>
+      </c>
+      <c r="O28" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="P28" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="Q28" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="R28" s="7">
+        <v>2</v>
+      </c>
+      <c r="S28" s="10">
+        <v>300000</v>
+      </c>
+      <c r="T28" s="10">
+        <v>300000</v>
+      </c>
+      <c r="U28" s="10">
+        <v>300000</v>
+      </c>
+      <c r="V28" s="10">
+        <v>300000</v>
+      </c>
+      <c r="W28" s="10">
+        <v>1000</v>
+      </c>
+      <c r="X28" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB28" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD28" s="10">
+        <v>300</v>
+      </c>
+      <c r="AE28" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="AF28" s="10">
+        <v>400</v>
+      </c>
+      <c r="AG28" s="10">
+        <v>1</v>
+      </c>
+      <c r="AH28" s="10">
+        <v>300</v>
+      </c>
+      <c r="AI28" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="AJ28" s="2">
+        <v>2010</v>
+      </c>
+      <c r="AK28" s="1">
+        <v>1</v>
+      </c>
+      <c r="AL28" s="1">
+        <v>1</v>
+      </c>
+      <c r="AM28" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="AN28" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="AO28" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="3:41">
+      <c r="C29" s="1">
+        <v>24</v>
+      </c>
+      <c r="D29" s="1">
+        <v>24</v>
+      </c>
+      <c r="E29" s="1">
+        <v>1</v>
+      </c>
+      <c r="F29" s="1">
+        <v>400</v>
+      </c>
+      <c r="G29" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="H29" s="2">
+        <v>2</v>
+      </c>
+      <c r="I29" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="J29" s="2">
+        <v>1</v>
+      </c>
+      <c r="K29" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="L29" s="2">
+        <v>2</v>
+      </c>
+      <c r="M29" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="N29" s="7">
+        <v>2</v>
+      </c>
+      <c r="O29" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="P29" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="Q29" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="R29" s="7">
+        <v>2</v>
+      </c>
+      <c r="S29" s="10">
+        <v>400000</v>
+      </c>
+      <c r="T29" s="10">
+        <v>400000</v>
+      </c>
+      <c r="U29" s="10">
+        <v>400000</v>
+      </c>
+      <c r="V29" s="10">
+        <v>400000</v>
+      </c>
+      <c r="W29" s="10">
+        <v>1000</v>
+      </c>
+      <c r="X29" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="10">
+        <v>300</v>
+      </c>
+      <c r="AE29" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="AF29" s="10">
+        <v>400</v>
+      </c>
+      <c r="AG29" s="10">
+        <v>1</v>
+      </c>
+      <c r="AH29" s="10">
+        <v>300</v>
+      </c>
+      <c r="AI29" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="AJ29" s="2">
+        <v>2013</v>
+      </c>
+      <c r="AK29" s="1">
+        <v>1</v>
+      </c>
+      <c r="AL29" s="1">
+        <v>1</v>
+      </c>
+      <c r="AM29" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="AN29" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="AO29" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="3:41">
+      <c r="M30" s="9"/>
+      <c r="N30" s="7"/>
+      <c r="O30" s="9"/>
+      <c r="P30" s="7"/>
+      <c r="Q30" s="9"/>
+      <c r="R30" s="7"/>
+      <c r="S30" s="2"/>
+      <c r="AF30" s="10"/>
+      <c r="AG30" s="10"/>
+      <c r="AH30" s="10"/>
+      <c r="AI30" s="10"/>
+    </row>
+    <row r="31" customHeight="1" spans="3:41">
+      <c r="M31" s="9"/>
+      <c r="N31" s="7"/>
+      <c r="O31" s="9"/>
+      <c r="P31" s="7"/>
+      <c r="Q31" s="9"/>
+      <c r="R31" s="7"/>
+      <c r="S31" s="2"/>
+      <c r="AF31" s="10"/>
+      <c r="AG31" s="10"/>
+      <c r="AH31" s="10"/>
+      <c r="AI31" s="10"/>
+    </row>
+    <row r="32" customHeight="1" spans="3:41">
+      <c r="M32" s="9"/>
+      <c r="N32" s="7"/>
+      <c r="O32" s="9"/>
+      <c r="P32" s="7"/>
+      <c r="Q32" s="9"/>
+      <c r="R32" s="7"/>
+      <c r="S32" s="2"/>
+      <c r="AD32" s="10"/>
+      <c r="AE32" s="10"/>
+      <c r="AF32" s="10"/>
+      <c r="AG32" s="10"/>
+      <c r="AH32" s="10"/>
+      <c r="AI32" s="10"/>
+    </row>
+    <row r="33" customHeight="1" spans="13:35">
+      <c r="M33" s="9"/>
+      <c r="N33" s="7"/>
+      <c r="O33" s="9"/>
+      <c r="P33" s="7"/>
+      <c r="Q33" s="9"/>
+      <c r="R33" s="7"/>
+      <c r="S33" s="2"/>
+      <c r="AD33" s="10"/>
+      <c r="AE33" s="10"/>
+      <c r="AF33" s="10"/>
+      <c r="AG33" s="10"/>
+      <c r="AH33" s="10"/>
+      <c r="AI33" s="10"/>
+    </row>
+    <row r="34" customHeight="1" spans="13:35">
+      <c r="M34" s="9"/>
+      <c r="N34" s="7"/>
+      <c r="O34" s="9"/>
+      <c r="P34" s="7"/>
+      <c r="Q34" s="9"/>
+      <c r="R34" s="7"/>
+      <c r="S34" s="2"/>
+      <c r="AD34" s="10"/>
+      <c r="AE34" s="10"/>
+      <c r="AF34" s="10"/>
+      <c r="AG34" s="10"/>
+      <c r="AH34" s="10"/>
+      <c r="AI34" s="10"/>
+    </row>
+    <row r="35" customHeight="1" spans="13:35">
+      <c r="M35" s="9"/>
+      <c r="N35" s="10"/>
+      <c r="O35" s="9"/>
+      <c r="P35" s="10"/>
+      <c r="Q35" s="9"/>
+      <c r="R35" s="10"/>
+      <c r="S35" s="2"/>
+      <c r="AF35" s="10"/>
+      <c r="AG35" s="10"/>
+      <c r="AH35" s="10"/>
+      <c r="AI35" s="10"/>
+    </row>
+    <row r="36" customHeight="1" spans="13:35">
+      <c r="M36" s="9"/>
+      <c r="N36" s="10"/>
+      <c r="O36" s="9"/>
+      <c r="P36" s="10"/>
+      <c r="Q36" s="9"/>
+      <c r="R36" s="10"/>
+      <c r="S36" s="2"/>
+      <c r="AF36" s="10"/>
+      <c r="AG36" s="10"/>
+      <c r="AH36" s="10"/>
+      <c r="AI36" s="10"/>
+    </row>
+    <row r="37" customHeight="1" spans="13:35">
+      <c r="M37" s="9"/>
+      <c r="N37" s="10"/>
+      <c r="O37" s="9"/>
+      <c r="P37" s="10"/>
+      <c r="Q37" s="9"/>
+      <c r="R37" s="10"/>
+      <c r="S37" s="2"/>
+      <c r="AD37" s="10"/>
+      <c r="AE37" s="10"/>
+      <c r="AF37" s="10"/>
+      <c r="AG37" s="10"/>
+      <c r="AH37" s="10"/>
+      <c r="AI37" s="10"/>
+    </row>
+    <row r="38" customHeight="1" spans="13:35">
+      <c r="M38" s="9"/>
+      <c r="N38" s="10"/>
+      <c r="O38" s="9"/>
+      <c r="P38" s="10"/>
+      <c r="Q38" s="9"/>
+      <c r="R38" s="10"/>
+      <c r="S38" s="2"/>
+      <c r="AD38" s="10"/>
+      <c r="AE38" s="10"/>
+      <c r="AF38" s="10"/>
+      <c r="AG38" s="10"/>
+      <c r="AH38" s="10"/>
+      <c r="AI38" s="10"/>
+    </row>
+    <row r="39" customHeight="1" spans="13:35">
+      <c r="M39" s="9"/>
+      <c r="N39" s="10"/>
+      <c r="O39" s="9"/>
+      <c r="P39" s="10"/>
+      <c r="Q39" s="9"/>
+      <c r="R39" s="10"/>
+      <c r="S39" s="2"/>
+      <c r="AD39" s="10"/>
+      <c r="AE39" s="10"/>
+      <c r="AF39" s="10"/>
+      <c r="AG39" s="10"/>
+      <c r="AH39" s="10"/>
+      <c r="AI39" s="10"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:W5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="K3:L3 AE3 K4 L4 AE4 H5 K5:L5 AE5 H3:H4 I3:I5 J3:J5 S3:S5 AD3:AD5 C3:D5 AJ3:AK5 E3:G5 M3:R5 T3:AC5 AF3:AI5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/PhantomAttrConfig.xlsx
+++ b/Excel/PhantomAttrConfig.xlsx
@@ -361,7 +361,7 @@
     <t>1E+10</t>
   </si>
   <si>
-    <t>1012,2003,2007,3008</t>
+    <t>1012,2003,2007</t>
   </si>
   <si>
     <t>1004,2009,2007,1012</t>
@@ -1909,7 +1909,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="1">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="G6" s="1">
         <v>1000</v>
@@ -2019,7 +2019,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="1">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="G7" s="1">
         <v>50000</v>
@@ -2129,7 +2129,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="1">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="G8" s="1">
         <v>40000</v>
@@ -2239,7 +2239,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="1">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="G9" s="1">
         <v>100000</v>
@@ -2349,7 +2349,7 @@
         <v>1</v>
       </c>
       <c r="F10" s="1">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="G10" s="1">
         <v>100000</v>
@@ -2459,7 +2459,7 @@
         <v>1</v>
       </c>
       <c r="F11" s="1">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="G11" s="1">
         <v>100000</v>
@@ -2569,7 +2569,7 @@
         <v>1</v>
       </c>
       <c r="F12" s="1">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="G12" s="12" t="s">
         <v>58</v>
@@ -2688,7 +2688,7 @@
         <v>1</v>
       </c>
       <c r="F13" s="1">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="G13" s="12" t="s">
         <v>59</v>
@@ -2807,7 +2807,7 @@
         <v>1</v>
       </c>
       <c r="F14" s="1">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="G14" s="12" t="s">
         <v>59</v>
@@ -2926,7 +2926,7 @@
         <v>1</v>
       </c>
       <c r="F15" s="1">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="G15" s="12" t="s">
         <v>59</v>
@@ -3036,7 +3036,7 @@
         <v>1</v>
       </c>
       <c r="F16" s="1">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="G16" s="12" t="s">
         <v>59</v>
@@ -3146,7 +3146,7 @@
         <v>1</v>
       </c>
       <c r="F17" s="1">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="G17" s="12" t="s">
         <v>59</v>
@@ -3256,7 +3256,7 @@
         <v>1</v>
       </c>
       <c r="F18" s="1">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="G18" s="12" t="s">
         <v>59</v>
@@ -3366,7 +3366,7 @@
         <v>1</v>
       </c>
       <c r="F19" s="1">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="G19" s="12" t="s">
         <v>82</v>
@@ -3476,7 +3476,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="G20" s="12" t="s">
         <v>82</v>
@@ -3586,7 +3586,7 @@
         <v>1</v>
       </c>
       <c r="F21" s="1">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="G21" s="12" t="s">
         <v>82</v>
@@ -3696,7 +3696,7 @@
         <v>1</v>
       </c>
       <c r="F22" s="1">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>87</v>
@@ -3815,7 +3815,7 @@
         <v>1</v>
       </c>
       <c r="F23" s="1">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="G23" s="13" t="s">
         <v>87</v>
@@ -3934,7 +3934,7 @@
         <v>1</v>
       </c>
       <c r="F24" s="1">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="G24" s="13" t="s">
         <v>87</v>
@@ -4053,7 +4053,7 @@
         <v>1</v>
       </c>
       <c r="F25" s="1">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="G25" s="13" t="s">
         <v>96</v>
@@ -4172,7 +4172,7 @@
         <v>1</v>
       </c>
       <c r="F26" s="1">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="G26" s="13" t="s">
         <v>96</v>
@@ -4291,7 +4291,7 @@
         <v>1</v>
       </c>
       <c r="F27" s="1">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>96</v>
@@ -4410,7 +4410,7 @@
         <v>1</v>
       </c>
       <c r="F28" s="1">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="G28" s="13" t="s">
         <v>101</v>
@@ -4529,7 +4529,7 @@
         <v>1</v>
       </c>
       <c r="F29" s="1">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>104</v>
@@ -4644,7 +4644,6 @@
       <c r="P30" s="7"/>
       <c r="Q30" s="9"/>
       <c r="R30" s="7"/>
-      <c r="S30" s="2"/>
       <c r="AF30" s="10"/>
       <c r="AG30" s="10"/>
       <c r="AH30" s="10"/>
@@ -4657,7 +4656,6 @@
       <c r="P31" s="7"/>
       <c r="Q31" s="9"/>
       <c r="R31" s="7"/>
-      <c r="S31" s="2"/>
       <c r="AF31" s="10"/>
       <c r="AG31" s="10"/>
       <c r="AH31" s="10"/>
@@ -4670,7 +4668,6 @@
       <c r="P32" s="7"/>
       <c r="Q32" s="9"/>
       <c r="R32" s="7"/>
-      <c r="S32" s="2"/>
       <c r="AD32" s="10"/>
       <c r="AE32" s="10"/>
       <c r="AF32" s="10"/>
@@ -4685,7 +4682,6 @@
       <c r="P33" s="7"/>
       <c r="Q33" s="9"/>
       <c r="R33" s="7"/>
-      <c r="S33" s="2"/>
       <c r="AD33" s="10"/>
       <c r="AE33" s="10"/>
       <c r="AF33" s="10"/>
@@ -4700,7 +4696,6 @@
       <c r="P34" s="7"/>
       <c r="Q34" s="9"/>
       <c r="R34" s="7"/>
-      <c r="S34" s="2"/>
       <c r="AD34" s="10"/>
       <c r="AE34" s="10"/>
       <c r="AF34" s="10"/>
@@ -4715,7 +4710,6 @@
       <c r="P35" s="10"/>
       <c r="Q35" s="9"/>
       <c r="R35" s="10"/>
-      <c r="S35" s="2"/>
       <c r="AF35" s="10"/>
       <c r="AG35" s="10"/>
       <c r="AH35" s="10"/>
@@ -4728,7 +4722,6 @@
       <c r="P36" s="10"/>
       <c r="Q36" s="9"/>
       <c r="R36" s="10"/>
-      <c r="S36" s="2"/>
       <c r="AF36" s="10"/>
       <c r="AG36" s="10"/>
       <c r="AH36" s="10"/>
@@ -4741,7 +4734,6 @@
       <c r="P37" s="10"/>
       <c r="Q37" s="9"/>
       <c r="R37" s="10"/>
-      <c r="S37" s="2"/>
       <c r="AD37" s="10"/>
       <c r="AE37" s="10"/>
       <c r="AF37" s="10"/>
@@ -4756,7 +4748,6 @@
       <c r="P38" s="10"/>
       <c r="Q38" s="9"/>
       <c r="R38" s="10"/>
-      <c r="S38" s="2"/>
       <c r="AD38" s="10"/>
       <c r="AE38" s="10"/>
       <c r="AF38" s="10"/>
@@ -4771,7 +4762,6 @@
       <c r="P39" s="10"/>
       <c r="Q39" s="9"/>
       <c r="R39" s="10"/>
-      <c r="S39" s="2"/>
       <c r="AD39" s="10"/>
       <c r="AE39" s="10"/>
       <c r="AF39" s="10"/>
@@ -4781,7 +4771,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="K3:L3 AE3 K4 L4 AE4 H5 K5:L5 AE5 H3:H4 I3:I5 J3:J5 S3:S5 AD3:AD5 C3:D5 AJ3:AK5 E3:G5 M3:R5 T3:AC5 AF3:AI5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:AK5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/PhantomAttrConfig.xlsx
+++ b/Excel/PhantomAttrConfig.xlsx
@@ -86,7 +86,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="118">
   <si>
     <t>ID</t>
   </si>
@@ -407,6 +407,39 @@
   </si>
   <si>
     <t>破韧倍率</t>
+  </si>
+  <si>
+    <t>1E+130</t>
+  </si>
+  <si>
+    <t>1E+50</t>
+  </si>
+  <si>
+    <t>经验增幅</t>
+  </si>
+  <si>
+    <t>1E+110</t>
+  </si>
+  <si>
+    <t>1E+140</t>
+  </si>
+  <si>
+    <t>金币增幅</t>
+  </si>
+  <si>
+    <t>1E+120</t>
+  </si>
+  <si>
+    <t>1E+150</t>
+  </si>
+  <si>
+    <t>品质增幅</t>
+  </si>
+  <si>
+    <t>1E+160</t>
+  </si>
+  <si>
+    <t>爆率增幅</t>
   </si>
 </sst>
 </file>
@@ -601,12 +634,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1882,10 +1915,10 @@
         <v>40</v>
       </c>
       <c r="AK5" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="AL5" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
+      </c>
+      <c r="AL5" s="4" t="s">
+        <v>42</v>
       </c>
       <c r="AM5" s="6" t="s">
         <v>44</v>
@@ -4638,84 +4671,554 @@
       </c>
     </row>
     <row r="30" customHeight="1" spans="3:41">
-      <c r="M30" s="9"/>
-      <c r="N30" s="7"/>
-      <c r="O30" s="9"/>
-      <c r="P30" s="7"/>
-      <c r="Q30" s="9"/>
-      <c r="R30" s="7"/>
-      <c r="AF30" s="10"/>
-      <c r="AG30" s="10"/>
-      <c r="AH30" s="10"/>
-      <c r="AI30" s="10"/>
+      <c r="C30" s="1">
+        <v>25</v>
+      </c>
+      <c r="D30" s="1">
+        <v>25</v>
+      </c>
+      <c r="E30" s="1">
+        <v>1</v>
+      </c>
+      <c r="F30" s="1">
+        <v>300</v>
+      </c>
+      <c r="G30" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="H30" s="2">
+        <v>3</v>
+      </c>
+      <c r="I30" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="J30" s="2">
+        <v>1</v>
+      </c>
+      <c r="K30" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="L30" s="2">
+        <v>3</v>
+      </c>
+      <c r="M30" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="N30" s="2">
+        <v>3</v>
+      </c>
+      <c r="O30" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="P30" s="2">
+        <v>3</v>
+      </c>
+      <c r="Q30" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="R30" s="2">
+        <v>3</v>
+      </c>
+      <c r="S30" s="10">
+        <v>500000</v>
+      </c>
+      <c r="T30" s="10">
+        <v>500000</v>
+      </c>
+      <c r="U30" s="10">
+        <v>500000</v>
+      </c>
+      <c r="V30" s="10">
+        <v>500000</v>
+      </c>
+      <c r="W30" s="10">
+        <v>1000</v>
+      </c>
+      <c r="X30" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA30" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB30" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC30" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD30" s="10">
+        <v>300</v>
+      </c>
+      <c r="AE30" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="AF30" s="10">
+        <v>500</v>
+      </c>
+      <c r="AG30" s="10">
+        <v>1</v>
+      </c>
+      <c r="AH30" s="10">
+        <v>400</v>
+      </c>
+      <c r="AI30" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="AJ30" s="2">
+        <v>50</v>
+      </c>
+      <c r="AK30" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="AL30" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="AM30" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="AN30" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="AO30" s="1" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="31" customHeight="1" spans="3:41">
-      <c r="M31" s="9"/>
-      <c r="N31" s="7"/>
-      <c r="O31" s="9"/>
-      <c r="P31" s="7"/>
-      <c r="Q31" s="9"/>
-      <c r="R31" s="7"/>
-      <c r="AF31" s="10"/>
-      <c r="AG31" s="10"/>
-      <c r="AH31" s="10"/>
-      <c r="AI31" s="10"/>
+      <c r="C31" s="1">
+        <v>26</v>
+      </c>
+      <c r="D31" s="1">
+        <v>26</v>
+      </c>
+      <c r="E31" s="1">
+        <v>1</v>
+      </c>
+      <c r="F31" s="1">
+        <v>300</v>
+      </c>
+      <c r="G31" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="H31" s="2">
+        <v>3.1</v>
+      </c>
+      <c r="I31" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="J31" s="2">
+        <v>1</v>
+      </c>
+      <c r="K31" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="L31" s="2">
+        <v>3.1</v>
+      </c>
+      <c r="M31" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="N31" s="2">
+        <v>3.1</v>
+      </c>
+      <c r="O31" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="P31" s="2">
+        <v>3.1</v>
+      </c>
+      <c r="Q31" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="R31" s="2">
+        <v>3.1</v>
+      </c>
+      <c r="S31" s="10">
+        <v>600000</v>
+      </c>
+      <c r="T31" s="10">
+        <v>600000</v>
+      </c>
+      <c r="U31" s="10">
+        <v>600000</v>
+      </c>
+      <c r="V31" s="10">
+        <v>600000</v>
+      </c>
+      <c r="W31" s="10">
+        <v>1000</v>
+      </c>
+      <c r="X31" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA31" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB31" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD31" s="10">
+        <v>300</v>
+      </c>
+      <c r="AE31" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="AF31" s="10">
+        <v>600</v>
+      </c>
+      <c r="AG31" s="10">
+        <v>1</v>
+      </c>
+      <c r="AH31" s="10">
+        <v>500</v>
+      </c>
+      <c r="AI31" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="AJ31" s="2">
+        <v>51</v>
+      </c>
+      <c r="AK31" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="AL31" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="AM31" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="AN31" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="AO31" s="1" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="32" customHeight="1" spans="3:41">
-      <c r="M32" s="9"/>
-      <c r="N32" s="7"/>
-      <c r="O32" s="9"/>
-      <c r="P32" s="7"/>
-      <c r="Q32" s="9"/>
-      <c r="R32" s="7"/>
-      <c r="AD32" s="10"/>
-      <c r="AE32" s="10"/>
-      <c r="AF32" s="10"/>
-      <c r="AG32" s="10"/>
-      <c r="AH32" s="10"/>
-      <c r="AI32" s="10"/>
+      <c r="C32" s="1">
+        <v>27</v>
+      </c>
+      <c r="D32" s="1">
+        <v>27</v>
+      </c>
+      <c r="E32" s="1">
+        <v>1</v>
+      </c>
+      <c r="F32" s="1">
+        <v>300</v>
+      </c>
+      <c r="G32" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="H32" s="2">
+        <v>3.2</v>
+      </c>
+      <c r="I32" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="J32" s="2">
+        <v>1</v>
+      </c>
+      <c r="K32" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="L32" s="2">
+        <v>3.2</v>
+      </c>
+      <c r="M32" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="N32" s="2">
+        <v>3.2</v>
+      </c>
+      <c r="O32" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="P32" s="2">
+        <v>3.2</v>
+      </c>
+      <c r="Q32" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="R32" s="2">
+        <v>3.2</v>
+      </c>
+      <c r="S32" s="10">
+        <v>700000</v>
+      </c>
+      <c r="T32" s="10">
+        <v>700000</v>
+      </c>
+      <c r="U32" s="10">
+        <v>700000</v>
+      </c>
+      <c r="V32" s="10">
+        <v>700000</v>
+      </c>
+      <c r="W32" s="10">
+        <v>1000</v>
+      </c>
+      <c r="X32" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="10">
+        <v>300</v>
+      </c>
+      <c r="AE32" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="AF32" s="10">
+        <v>700</v>
+      </c>
+      <c r="AG32" s="10">
+        <v>1</v>
+      </c>
+      <c r="AH32" s="10">
+        <v>600</v>
+      </c>
+      <c r="AI32" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="AJ32" s="2">
+        <v>55</v>
+      </c>
+      <c r="AK32" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="AL32" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="AM32" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="AN32" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="AO32" s="1" t="s">
+        <v>115</v>
+      </c>
     </row>
-    <row r="33" customHeight="1" spans="13:35">
-      <c r="M33" s="9"/>
-      <c r="N33" s="7"/>
-      <c r="O33" s="9"/>
-      <c r="P33" s="7"/>
-      <c r="Q33" s="9"/>
-      <c r="R33" s="7"/>
-      <c r="AD33" s="10"/>
-      <c r="AE33" s="10"/>
-      <c r="AF33" s="10"/>
-      <c r="AG33" s="10"/>
-      <c r="AH33" s="10"/>
-      <c r="AI33" s="10"/>
+    <row r="33" customHeight="1" spans="3:41">
+      <c r="C33" s="1">
+        <v>28</v>
+      </c>
+      <c r="D33" s="1">
+        <v>28</v>
+      </c>
+      <c r="E33" s="1">
+        <v>1</v>
+      </c>
+      <c r="F33" s="1">
+        <v>300</v>
+      </c>
+      <c r="G33" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="H33" s="2">
+        <v>3.3</v>
+      </c>
+      <c r="I33" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="J33" s="2">
+        <v>1</v>
+      </c>
+      <c r="K33" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="L33" s="2">
+        <v>3.3</v>
+      </c>
+      <c r="M33" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="N33" s="2">
+        <v>3.3</v>
+      </c>
+      <c r="O33" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="P33" s="2">
+        <v>3.3</v>
+      </c>
+      <c r="Q33" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="R33" s="2">
+        <v>3.3</v>
+      </c>
+      <c r="S33" s="10">
+        <v>800000</v>
+      </c>
+      <c r="T33" s="10">
+        <v>800000</v>
+      </c>
+      <c r="U33" s="10">
+        <v>800000</v>
+      </c>
+      <c r="V33" s="10">
+        <v>800000</v>
+      </c>
+      <c r="W33" s="10">
+        <v>1000</v>
+      </c>
+      <c r="X33" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y33" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z33" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA33" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB33" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC33" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD33" s="10">
+        <v>300</v>
+      </c>
+      <c r="AE33" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="AF33" s="10">
+        <v>800</v>
+      </c>
+      <c r="AG33" s="10">
+        <v>1</v>
+      </c>
+      <c r="AH33" s="10">
+        <v>700</v>
+      </c>
+      <c r="AI33" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="AJ33" s="2">
+        <v>54</v>
+      </c>
+      <c r="AK33" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="AL33" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="AM33" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="AN33" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="AO33" s="1" t="s">
+        <v>117</v>
+      </c>
     </row>
-    <row r="34" customHeight="1" spans="13:35">
-      <c r="M34" s="9"/>
+    <row r="34" customHeight="1" spans="3:41">
+      <c r="G34" s="7"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="7"/>
+      <c r="J34" s="2"/>
+      <c r="K34" s="7"/>
+      <c r="L34" s="2"/>
+      <c r="M34" s="7"/>
       <c r="N34" s="7"/>
       <c r="O34" s="9"/>
       <c r="P34" s="7"/>
       <c r="Q34" s="9"/>
       <c r="R34" s="7"/>
+      <c r="S34" s="10"/>
+      <c r="T34" s="10"/>
+      <c r="U34" s="10"/>
+      <c r="V34" s="10"/>
+      <c r="W34" s="10"/>
+      <c r="X34" s="2"/>
+      <c r="Y34" s="2"/>
+      <c r="Z34" s="2"/>
+      <c r="AA34" s="2"/>
+      <c r="AB34" s="2"/>
+      <c r="AC34" s="2"/>
       <c r="AD34" s="10"/>
       <c r="AE34" s="10"/>
       <c r="AF34" s="10"/>
       <c r="AG34" s="10"/>
       <c r="AH34" s="10"/>
       <c r="AI34" s="10"/>
+      <c r="AJ34" s="2"/>
+      <c r="AK34" s="1"/>
+      <c r="AL34" s="1"/>
+      <c r="AM34" s="11"/>
+      <c r="AN34" s="10"/>
     </row>
-    <row r="35" customHeight="1" spans="13:35">
-      <c r="M35" s="9"/>
-      <c r="N35" s="10"/>
+    <row r="35" customHeight="1" spans="3:41">
+      <c r="G35" s="7"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="7"/>
+      <c r="J35" s="2"/>
+      <c r="K35" s="7"/>
+      <c r="L35" s="2"/>
+      <c r="M35" s="7"/>
+      <c r="N35" s="7"/>
       <c r="O35" s="9"/>
-      <c r="P35" s="10"/>
+      <c r="P35" s="7"/>
       <c r="Q35" s="9"/>
-      <c r="R35" s="10"/>
+      <c r="R35" s="7"/>
+      <c r="S35" s="10"/>
+      <c r="T35" s="10"/>
+      <c r="U35" s="10"/>
+      <c r="V35" s="10"/>
+      <c r="W35" s="10"/>
+      <c r="X35" s="2"/>
+      <c r="Y35" s="2"/>
+      <c r="Z35" s="2"/>
+      <c r="AA35" s="2"/>
+      <c r="AB35" s="2"/>
+      <c r="AC35" s="2"/>
+      <c r="AD35" s="10"/>
+      <c r="AE35" s="10"/>
       <c r="AF35" s="10"/>
       <c r="AG35" s="10"/>
       <c r="AH35" s="10"/>
       <c r="AI35" s="10"/>
+      <c r="AJ35" s="2"/>
+      <c r="AK35" s="1"/>
+      <c r="AL35" s="1"/>
+      <c r="AM35" s="11"/>
+      <c r="AN35" s="10"/>
     </row>
-    <row r="36" customHeight="1" spans="13:35">
+    <row r="36" customHeight="1" spans="3:41">
       <c r="M36" s="9"/>
       <c r="N36" s="10"/>
       <c r="O36" s="9"/>
@@ -4727,7 +5230,7 @@
       <c r="AH36" s="10"/>
       <c r="AI36" s="10"/>
     </row>
-    <row r="37" customHeight="1" spans="13:35">
+    <row r="37" customHeight="1" spans="3:41">
       <c r="M37" s="9"/>
       <c r="N37" s="10"/>
       <c r="O37" s="9"/>
@@ -4741,7 +5244,7 @@
       <c r="AH37" s="10"/>
       <c r="AI37" s="10"/>
     </row>
-    <row r="38" customHeight="1" spans="13:35">
+    <row r="38" customHeight="1" spans="3:41">
       <c r="M38" s="9"/>
       <c r="N38" s="10"/>
       <c r="O38" s="9"/>
@@ -4755,7 +5258,7 @@
       <c r="AH38" s="10"/>
       <c r="AI38" s="10"/>
     </row>
-    <row r="39" customHeight="1" spans="13:35">
+    <row r="39" customHeight="1" spans="3:41">
       <c r="M39" s="9"/>
       <c r="N39" s="10"/>
       <c r="O39" s="9"/>
@@ -4771,7 +5274,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:AK5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="AL5 C3:AK5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/PhantomAttrConfig.xlsx
+++ b/Excel/PhantomAttrConfig.xlsx
@@ -634,12 +634,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -5009,7 +5009,7 @@
         <v>0.5</v>
       </c>
       <c r="AJ32" s="2">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="AK32" s="1">
         <v>0.1</v>
@@ -5128,7 +5128,7 @@
         <v>0.5</v>
       </c>
       <c r="AJ33" s="2">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="AK33" s="1">
         <v>0.1</v>
@@ -5148,11 +5148,8 @@
     </row>
     <row r="34" customHeight="1" spans="3:41">
       <c r="G34" s="7"/>
-      <c r="H34" s="2"/>
       <c r="I34" s="7"/>
-      <c r="J34" s="2"/>
       <c r="K34" s="7"/>
-      <c r="L34" s="2"/>
       <c r="M34" s="7"/>
       <c r="N34" s="7"/>
       <c r="O34" s="9"/>
@@ -5164,31 +5161,20 @@
       <c r="U34" s="10"/>
       <c r="V34" s="10"/>
       <c r="W34" s="10"/>
-      <c r="X34" s="2"/>
-      <c r="Y34" s="2"/>
-      <c r="Z34" s="2"/>
-      <c r="AA34" s="2"/>
-      <c r="AB34" s="2"/>
-      <c r="AC34" s="2"/>
       <c r="AD34" s="10"/>
       <c r="AE34" s="10"/>
       <c r="AF34" s="10"/>
       <c r="AG34" s="10"/>
       <c r="AH34" s="10"/>
       <c r="AI34" s="10"/>
-      <c r="AJ34" s="2"/>
       <c r="AK34" s="1"/>
-      <c r="AL34" s="1"/>
       <c r="AM34" s="11"/>
       <c r="AN34" s="10"/>
     </row>
     <row r="35" customHeight="1" spans="3:41">
       <c r="G35" s="7"/>
-      <c r="H35" s="2"/>
       <c r="I35" s="7"/>
-      <c r="J35" s="2"/>
       <c r="K35" s="7"/>
-      <c r="L35" s="2"/>
       <c r="M35" s="7"/>
       <c r="N35" s="7"/>
       <c r="O35" s="9"/>
@@ -5200,21 +5186,13 @@
       <c r="U35" s="10"/>
       <c r="V35" s="10"/>
       <c r="W35" s="10"/>
-      <c r="X35" s="2"/>
-      <c r="Y35" s="2"/>
-      <c r="Z35" s="2"/>
-      <c r="AA35" s="2"/>
-      <c r="AB35" s="2"/>
-      <c r="AC35" s="2"/>
       <c r="AD35" s="10"/>
       <c r="AE35" s="10"/>
       <c r="AF35" s="10"/>
       <c r="AG35" s="10"/>
       <c r="AH35" s="10"/>
       <c r="AI35" s="10"/>
-      <c r="AJ35" s="2"/>
       <c r="AK35" s="1"/>
-      <c r="AL35" s="1"/>
       <c r="AM35" s="11"/>
       <c r="AN35" s="10"/>
     </row>
@@ -5274,7 +5252,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="AL5 C3:AK5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C5:AL5 C3:AK4" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
